--- a/project requirements spreadsheet.xlsx
+++ b/project requirements spreadsheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Documents\__ School\CS 3300- Software Development\Project (Group 1)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B15907A1-EAE0-4607-8B7A-A616537C7F23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CEAFA44-663C-4789-9E2F-DB2D92A94F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{CAB5D44A-E176-404C-B398-BEAD2D9E6884}"/>
+    <workbookView xWindow="-28908" yWindow="-108" windowWidth="29016" windowHeight="15972" xr2:uid="{CAB5D44A-E176-404C-B398-BEAD2D9E6884}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="97">
   <si>
     <t>Intro to Software Engineering</t>
   </si>
@@ -323,6 +323,18 @@
     <t>Notes: "Flags resolved" column not included. 
          - Submission issues included in comments. 
          - Bugs or issues in submissions moved to future iterations Requirements</t>
+  </si>
+  <si>
+    <t>Improve Comments on Core Classes</t>
+  </si>
+  <si>
+    <t>Improve Comments on Puzzle Classes</t>
+  </si>
+  <si>
+    <t>J Hong / T Fox</t>
+  </si>
+  <si>
+    <t>Add to the puzzle description reason puzzle is being solved</t>
   </si>
 </sst>
 </file>
@@ -577,7 +589,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -783,6 +795,30 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -807,9 +843,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -822,26 +855,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1185,121 +1200,121 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B900A37F-814E-4AF4-9047-E946E2A67EEB}">
   <dimension ref="A1:M170"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.5703125" style="6" customWidth="1"/>
-    <col min="2" max="2" width="61.28515625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="6" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.7109375" style="6" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" style="6" customWidth="1"/>
-    <col min="9" max="11" width="12.7109375" style="6" customWidth="1"/>
-    <col min="12" max="12" width="25.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="173.85546875" style="25" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="13"/>
+    <col min="1" max="1" width="15.5546875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="61.33203125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.6640625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" style="6" customWidth="1"/>
+    <col min="9" max="11" width="12.6640625" style="6" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" style="6" customWidth="1"/>
+    <col min="13" max="13" width="173.88671875" style="25" customWidth="1"/>
+    <col min="14" max="16384" width="9.109375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+    <row r="1" spans="1:13" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="79" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="72"/>
+      <c r="B1" s="80"/>
       <c r="C1" s="29"/>
-      <c r="D1" s="78" t="s">
+      <c r="D1" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
       <c r="L1" s="29"/>
       <c r="M1" s="31"/>
     </row>
-    <row r="2" spans="1:13" s="32" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="73" t="s">
+    <row r="2" spans="1:13" s="32" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="74"/>
+      <c r="B2" s="82"/>
       <c r="C2" s="29"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="85"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="52"/>
       <c r="B3" s="39"/>
       <c r="C3" s="13"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="85"/>
       <c r="L3" s="13"/>
       <c r="M3" s="13"/>
     </row>
-    <row r="4" spans="1:13" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="53" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="78"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="78"/>
-      <c r="J4" s="78"/>
-      <c r="K4" s="78"/>
-    </row>
-    <row r="5" spans="1:13" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D4" s="85"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="85"/>
+    </row>
+    <row r="5" spans="1:13" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="53" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
-      <c r="K5" s="78"/>
-    </row>
-    <row r="6" spans="1:13" s="7" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D5" s="85"/>
+      <c r="E5" s="85"/>
+      <c r="F5" s="85"/>
+      <c r="G5" s="85"/>
+      <c r="H5" s="85"/>
+      <c r="I5" s="85"/>
+      <c r="J5" s="85"/>
+      <c r="K5" s="85"/>
+    </row>
+    <row r="6" spans="1:13" s="7" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="54" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="D6" s="78"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78"/>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
-      <c r="J6" s="78"/>
-      <c r="K6" s="78"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="85"/>
+      <c r="F6" s="85"/>
+      <c r="G6" s="85"/>
+      <c r="H6" s="85"/>
+      <c r="I6" s="85"/>
+      <c r="J6" s="85"/>
+      <c r="K6" s="85"/>
       <c r="L6" s="1"/>
       <c r="M6" s="33"/>
     </row>
-    <row r="7" spans="1:13" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="55"/>
       <c r="B7" s="2"/>
       <c r="C7" s="1"/>
@@ -1314,100 +1329,100 @@
       <c r="L7" s="1"/>
       <c r="M7" s="33"/>
     </row>
-    <row r="8" spans="1:13" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="79" t="s">
+    <row r="8" spans="1:13" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="79"/>
-      <c r="C8" s="79"/>
-      <c r="D8" s="79"/>
-      <c r="E8" s="79"/>
-      <c r="F8" s="79"/>
-      <c r="G8" s="79"/>
-      <c r="H8" s="79"/>
-      <c r="I8" s="79"/>
-      <c r="J8" s="79"/>
-      <c r="K8" s="79"/>
-      <c r="L8" s="79"/>
-      <c r="M8" s="79"/>
-    </row>
-    <row r="9" spans="1:13" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="86"/>
+      <c r="C8" s="86"/>
+      <c r="D8" s="86"/>
+      <c r="E8" s="86"/>
+      <c r="F8" s="86"/>
+      <c r="G8" s="86"/>
+      <c r="H8" s="86"/>
+      <c r="I8" s="86"/>
+      <c r="J8" s="86"/>
+      <c r="K8" s="86"/>
+      <c r="L8" s="86"/>
+      <c r="M8" s="86"/>
+    </row>
+    <row r="9" spans="1:13" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="79" t="s">
+      <c r="C9" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="79"/>
-      <c r="E9" s="79"/>
-      <c r="F9" s="79"/>
+      <c r="D9" s="86"/>
+      <c r="E9" s="86"/>
+      <c r="F9" s="86"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="79" t="s">
+      <c r="H9" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="79"/>
-      <c r="J9" s="79"/>
-      <c r="K9" s="79"/>
-      <c r="L9" s="80" t="s">
+      <c r="I9" s="86"/>
+      <c r="J9" s="86"/>
+      <c r="K9" s="86"/>
+      <c r="L9" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="M9" s="81" t="s">
+      <c r="M9" s="88" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:13" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="77" t="s">
+      <c r="C10" s="76" t="s">
         <v>21</v>
       </c>
       <c r="D10" s="1"/>
-      <c r="E10" s="77" t="s">
+      <c r="E10" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="77" t="s">
+      <c r="F10" s="76" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="77" t="s">
+      <c r="G10" s="76" t="s">
         <v>61</v>
       </c>
-      <c r="H10" s="77" t="s">
+      <c r="H10" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="I10" s="77" t="s">
+      <c r="I10" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="77" t="s">
+      <c r="J10" s="76" t="s">
         <v>5</v>
       </c>
       <c r="K10" s="1"/>
-      <c r="L10" s="80"/>
-      <c r="M10" s="81"/>
-    </row>
-    <row r="11" spans="1:13" s="7" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L10" s="87"/>
+      <c r="M10" s="88"/>
+    </row>
+    <row r="11" spans="1:13" s="7" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="77"/>
+      <c r="C11" s="76"/>
       <c r="D11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="77"/>
-      <c r="J11" s="77"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76"/>
+      <c r="J11" s="76"/>
       <c r="K11" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="L11" s="80"/>
-      <c r="M11" s="81"/>
-    </row>
-    <row r="12" spans="1:13" s="68" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="75" t="s">
+      <c r="L11" s="87"/>
+      <c r="M11" s="88"/>
+    </row>
+    <row r="12" spans="1:13" s="68" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="83" t="s">
         <v>40</v>
       </c>
       <c r="B12" s="63"/>
@@ -1433,8 +1448,8 @@
       <c r="L12" s="66"/>
       <c r="M12" s="67"/>
     </row>
-    <row r="13" spans="1:13" s="3" customFormat="1" ht="61.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="76"/>
+    <row r="13" spans="1:13" s="3" customFormat="1" ht="61.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="84"/>
       <c r="B13" s="8"/>
       <c r="C13" s="10"/>
       <c r="D13" s="10" t="s">
@@ -1454,7 +1469,7 @@
       <c r="L13" s="11"/>
       <c r="M13" s="36"/>
     </row>
-    <row r="14" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="56">
         <v>0</v>
       </c>
@@ -1486,7 +1501,7 @@
       <c r="L14" s="22"/>
       <c r="M14" s="24"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="57">
         <f>A14+1</f>
         <v>1</v>
@@ -1512,7 +1527,7 @@
       </c>
       <c r="L15" s="12"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="57">
         <f t="shared" ref="A16:A33" si="0">A15+1</f>
         <v>2</v>
@@ -1538,7 +1553,7 @@
       </c>
       <c r="L16" s="12"/>
     </row>
-    <row r="17" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="57">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1546,8 +1561,8 @@
       <c r="B17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="28" t="s">
-        <v>55</v>
+      <c r="C17" s="10" t="s">
+        <v>95</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>47</v>
@@ -1564,7 +1579,7 @@
       </c>
       <c r="L17" s="12"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="57">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1590,7 +1605,7 @@
       </c>
       <c r="L18" s="12"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="57">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1616,7 +1631,7 @@
       </c>
       <c r="L19" s="12"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="57">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1642,7 +1657,7 @@
       </c>
       <c r="L20" s="12"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="57">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1668,7 +1683,7 @@
       </c>
       <c r="L21" s="12"/>
     </row>
-    <row r="22" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="57">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1676,8 +1691,8 @@
       <c r="B22" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="28" t="s">
-        <v>55</v>
+      <c r="C22" s="89" t="s">
+        <v>44</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>47</v>
@@ -1694,7 +1709,7 @@
       </c>
       <c r="L22" s="12"/>
     </row>
-    <row r="23" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="57">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1720,7 +1735,7 @@
       </c>
       <c r="L23" s="12"/>
     </row>
-    <row r="24" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="57">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1746,7 +1761,7 @@
       </c>
       <c r="L24" s="12"/>
     </row>
-    <row r="25" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="57">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1772,7 +1787,7 @@
       </c>
       <c r="L25" s="12"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="57">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1801,7 +1816,7 @@
       </c>
       <c r="L26" s="12"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="57">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1824,7 +1839,7 @@
       </c>
       <c r="L27" s="12"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="57">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1847,7 +1862,7 @@
       </c>
       <c r="L28" s="12"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="57">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1870,7 +1885,7 @@
       </c>
       <c r="L29" s="12"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="57">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1893,7 +1908,7 @@
       </c>
       <c r="L30" s="12"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="57">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1916,7 +1931,7 @@
       </c>
       <c r="L31" s="12"/>
     </row>
-    <row r="32" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="57">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1939,7 +1954,7 @@
       </c>
       <c r="L32" s="12"/>
     </row>
-    <row r="33" spans="1:13" s="15" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" s="15" customFormat="1" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="58">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1968,7 +1983,7 @@
       <c r="L33" s="14"/>
       <c r="M33" s="26"/>
     </row>
-    <row r="34" spans="1:13" s="19" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" s="19" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="59">
         <f>IF(D34=D33,A33+1,(D34*100))</f>
         <v>0</v>
@@ -2001,7 +2016,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="60">
         <f t="shared" ref="A35:A45" si="2">IF(D35=D34,A34+1,(D35*100))</f>
         <v>1</v>
@@ -2026,11 +2041,11 @@
         <v>-20</v>
       </c>
       <c r="L35" s="12"/>
-      <c r="M35" s="69" t="s">
+      <c r="M35" s="77" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="60">
         <f t="shared" si="2"/>
         <v>2</v>
@@ -2055,9 +2070,9 @@
         <v>-20</v>
       </c>
       <c r="L36" s="12"/>
-      <c r="M36" s="70"/>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M36" s="78"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="60">
         <f t="shared" si="2"/>
         <v>3</v>
@@ -2082,9 +2097,9 @@
         <v>-20</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="M37" s="70"/>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M37" s="78"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="60">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -2109,9 +2124,9 @@
         <v>-20</v>
       </c>
       <c r="L38" s="12"/>
-      <c r="M38" s="70"/>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M38" s="78"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="60">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -2136,9 +2151,9 @@
         <v>-20</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="70"/>
-    </row>
-    <row r="40" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="M39" s="78"/>
+    </row>
+    <row r="40" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" s="60">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -2167,7 +2182,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="60">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -2196,7 +2211,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="60">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -2225,7 +2240,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="60">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -2254,7 +2269,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="60">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -2283,7 +2298,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="45" spans="1:13" s="15" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" s="15" customFormat="1" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="61">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -2316,7 +2331,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="46" spans="1:13" s="49" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" s="49" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="62">
         <f>IF(D46=D44,A44+1,(D46*100))</f>
         <v>100</v>
@@ -2346,7 +2361,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="47" spans="1:13" s="19" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" s="19" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="59">
         <f>IF(D47=D45,A45+1,(D47*100))</f>
         <v>100</v>
@@ -2374,37 +2389,37 @@
       <c r="K47" s="18"/>
       <c r="L47" s="22"/>
     </row>
-    <row r="48" spans="1:13" s="88" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="82">
+    <row r="48" spans="1:13" s="75" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="69">
         <f>IF(B48="","",IF(D48=D47,A47+1,(D48*100)))</f>
         <v>101</v>
       </c>
-      <c r="B48" s="83" t="str">
+      <c r="B48" s="70" t="str">
         <f>"Iteration "&amp;D48-1&amp;" Test Report (Optional)"</f>
         <v>Iteration 0 Test Report (Optional)</v>
       </c>
-      <c r="C48" s="84" t="s">
+      <c r="C48" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="D48" s="84">
+      <c r="D48" s="71">
         <v>1</v>
       </c>
-      <c r="E48" s="85">
+      <c r="E48" s="72">
         <v>45596</v>
       </c>
-      <c r="F48" s="86"/>
-      <c r="G48" s="84">
+      <c r="F48" s="73"/>
+      <c r="G48" s="71">
         <f>IF(B48="","",IF(AND(E48&gt;0,F48&gt;0),F48-E48,0))</f>
         <v>0</v>
       </c>
-      <c r="H48" s="84"/>
-      <c r="I48" s="84"/>
-      <c r="J48" s="84"/>
-      <c r="K48" s="84"/>
-      <c r="L48" s="85"/>
-      <c r="M48" s="87"/>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H48" s="71"/>
+      <c r="I48" s="71"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="71"/>
+      <c r="L48" s="72"/>
+      <c r="M48" s="74"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="60">
         <f t="shared" ref="A49:A112" si="3">IF(B49="","",IF(D49=D48,A48+1,(D49*100)))</f>
         <v>102</v>
@@ -2430,7 +2445,7 @@
       </c>
       <c r="L49" s="12"/>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="60">
         <f t="shared" si="3"/>
         <v>103</v>
@@ -2456,7 +2471,7 @@
       </c>
       <c r="L50" s="12"/>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="60">
         <f t="shared" si="3"/>
         <v>104</v>
@@ -2482,7 +2497,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="60">
         <f t="shared" si="3"/>
         <v>105</v>
@@ -2508,7 +2523,7 @@
       </c>
       <c r="L52" s="12"/>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="60">
         <f t="shared" si="3"/>
         <v>106</v>
@@ -2531,7 +2546,7 @@
       </c>
       <c r="L53" s="12"/>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="60">
         <f t="shared" si="3"/>
         <v>107</v>
@@ -2554,7 +2569,7 @@
       </c>
       <c r="L54" s="12"/>
     </row>
-    <row r="55" spans="1:13" s="15" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" s="15" customFormat="1" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="61">
         <f t="shared" si="3"/>
         <v>108</v>
@@ -2583,7 +2598,7 @@
       <c r="L55" s="14"/>
       <c r="M55" s="26"/>
     </row>
-    <row r="56" spans="1:13" s="16" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" s="16" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="51">
         <f t="shared" si="3"/>
         <v>200</v>
@@ -2599,8 +2614,7 @@
         <v>2</v>
       </c>
       <c r="E56" s="50">
-        <f>IF(B56="","",IF(D56=D55,E55,E55+14))</f>
-        <v>45610</v>
+        <v>45601</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="6">
@@ -2614,7 +2628,7 @@
       <c r="L56" s="12"/>
       <c r="M56" s="34"/>
     </row>
-    <row r="57" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="51">
         <f t="shared" si="3"/>
         <v>201</v>
@@ -2631,7 +2645,7 @@
       </c>
       <c r="E57" s="50">
         <f t="shared" ref="E57:E120" si="5">IF(B57="","",IF(D57=D56,E56,E56+14))</f>
-        <v>45610</v>
+        <v>45601</v>
       </c>
       <c r="G57" s="6">
         <f t="shared" si="4"/>
@@ -2639,7 +2653,7 @@
       </c>
       <c r="L57" s="12"/>
     </row>
-    <row r="58" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="51">
         <f t="shared" si="3"/>
         <v>202</v>
@@ -2655,7 +2669,7 @@
       </c>
       <c r="E58" s="50">
         <f t="shared" si="5"/>
-        <v>45610</v>
+        <v>45601</v>
       </c>
       <c r="G58" s="6">
         <f t="shared" si="4"/>
@@ -2663,7 +2677,7 @@
       </c>
       <c r="L58" s="12"/>
     </row>
-    <row r="59" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="51">
         <f t="shared" si="3"/>
         <v>203</v>
@@ -2679,7 +2693,7 @@
       </c>
       <c r="E59" s="50">
         <f t="shared" si="5"/>
-        <v>45610</v>
+        <v>45601</v>
       </c>
       <c r="G59" s="6">
         <f t="shared" si="4"/>
@@ -2687,1179 +2701,1191 @@
       </c>
       <c r="L59" s="12"/>
     </row>
-    <row r="60" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D60" s="6" t="str">
+    <row r="60" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A60" s="51">
+        <f t="shared" si="3"/>
+        <v>204</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D60" s="6">
         <f>IF(B60="","",D59)</f>
-        <v/>
-      </c>
-      <c r="E60" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G60" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L60" s="12" t="str">
-        <f t="shared" ref="L60:L112" si="6">IF(B60="","",IF(D60=D59,L59,IF(F60&gt;0,F60,"Not Delivered")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D61" s="6" t="str">
-        <f t="shared" ref="D61:D124" si="7">IF(B61="","",D60)</f>
-        <v/>
-      </c>
-      <c r="E61" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G61" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L61" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="62" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D62" s="6" t="str">
+        <v>2</v>
+      </c>
+      <c r="E60" s="50">
+        <f t="shared" si="5"/>
+        <v>45601</v>
+      </c>
+      <c r="G60" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L60" s="12"/>
+    </row>
+    <row r="61" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A61" s="51">
+        <f t="shared" si="3"/>
+        <v>205</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D61" s="6">
+        <f t="shared" ref="D61:D124" si="6">IF(B61="","",D60)</f>
+        <v>2</v>
+      </c>
+      <c r="E61" s="50">
+        <f t="shared" si="5"/>
+        <v>45601</v>
+      </c>
+      <c r="G61" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L61" s="12"/>
+    </row>
+    <row r="62" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A62" s="51">
+        <f t="shared" si="3"/>
+        <v>206</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D62" s="6">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="E62" s="50">
+        <f t="shared" si="5"/>
+        <v>45601</v>
+      </c>
+      <c r="G62" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L62" s="12">
+        <f t="shared" ref="L60:L112" si="7">IF(B62="","",IF(D62=D61,L61,IF(F62&gt;0,F62,"Not Delivered")))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A63" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D63" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E63" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G63" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L63" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E62" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G62" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L62" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="63" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D63" s="6" t="str">
+    </row>
+    <row r="64" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A64" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D64" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E64" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G64" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L64" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E63" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G63" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L63" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A64" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D64" s="6" t="str">
+    </row>
+    <row r="65" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A65" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D65" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E65" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G65" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L65" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E64" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G64" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L64" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="65" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D65" s="6" t="str">
+    </row>
+    <row r="66" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A66" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D66" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E66" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G66" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L66" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E65" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G65" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L65" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D66" s="6" t="str">
+    </row>
+    <row r="67" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A67" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D67" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E67" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G67" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L67" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E66" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G66" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L66" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D67" s="6" t="str">
+    </row>
+    <row r="68" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A68" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D68" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E68" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G68" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L68" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E67" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G67" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L67" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A68" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D68" s="6" t="str">
+    </row>
+    <row r="69" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A69" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D69" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E69" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G69" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L69" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E68" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G68" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L68" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="69" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A69" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D69" s="6" t="str">
+    </row>
+    <row r="70" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A70" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D70" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E70" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G70" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L70" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E69" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G69" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L69" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A70" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D70" s="6" t="str">
+    </row>
+    <row r="71" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D71" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E71" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G71" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L71" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E70" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G70" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L70" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A71" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D71" s="6" t="str">
+    </row>
+    <row r="72" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A72" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D72" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E72" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G72" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L72" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E71" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G71" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L71" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A72" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D72" s="6" t="str">
+    </row>
+    <row r="73" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A73" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D73" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E73" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G73" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L73" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E72" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G72" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L72" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D73" s="6" t="str">
+    </row>
+    <row r="74" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A74" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D74" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E74" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G74" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L74" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E73" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G73" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L73" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D74" s="6" t="str">
+    </row>
+    <row r="75" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A75" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D75" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E75" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G75" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L75" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E74" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G74" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L74" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="75" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A75" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D75" s="6" t="str">
+    </row>
+    <row r="76" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A76" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D76" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E76" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G76" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L76" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E75" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G75" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L75" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D76" s="6" t="str">
+    </row>
+    <row r="77" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A77" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D77" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E77" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G77" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L77" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E76" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G76" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L76" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A77" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D77" s="6" t="str">
+    </row>
+    <row r="78" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A78" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D78" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E78" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G78" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L78" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E77" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G77" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L77" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A78" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D78" s="6" t="str">
+    </row>
+    <row r="79" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A79" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D79" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E79" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G79" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L79" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E78" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G78" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L78" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="79" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D79" s="6" t="str">
+    </row>
+    <row r="80" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A80" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D80" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E80" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G80" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L80" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E79" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G79" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L79" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D80" s="6" t="str">
+    </row>
+    <row r="81" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A81" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D81" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E81" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G81" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L81" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E80" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G80" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L80" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="81" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A81" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D81" s="6" t="str">
+    </row>
+    <row r="82" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A82" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D82" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E82" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G82" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L82" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E81" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G81" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L81" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="82" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A82" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D82" s="6" t="str">
+    </row>
+    <row r="83" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A83" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D83" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E83" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G83" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L83" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E82" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G82" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L82" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="83" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A83" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D83" s="6" t="str">
+    </row>
+    <row r="84" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A84" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D84" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E84" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G84" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L84" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E83" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G83" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L83" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="84" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A84" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D84" s="6" t="str">
+    </row>
+    <row r="85" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A85" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D85" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E85" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G85" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L85" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E84" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G84" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L84" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="85" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A85" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D85" s="6" t="str">
+    </row>
+    <row r="86" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A86" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D86" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E86" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G86" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L86" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E85" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G85" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L85" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="86" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A86" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D86" s="6" t="str">
+    </row>
+    <row r="87" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A87" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D87" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E87" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G87" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L87" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E86" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G86" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L86" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="87" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A87" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D87" s="6" t="str">
+    </row>
+    <row r="88" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A88" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D88" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E88" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G88" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L88" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E87" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G87" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L87" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="88" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A88" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D88" s="6" t="str">
+    </row>
+    <row r="89" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A89" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D89" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E89" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G89" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L89" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E88" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G88" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L88" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="89" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A89" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D89" s="6" t="str">
+    </row>
+    <row r="90" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A90" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D90" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E90" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G90" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L90" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E89" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G89" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L89" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="90" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A90" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D90" s="6" t="str">
+    </row>
+    <row r="91" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A91" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D91" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E91" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G91" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L91" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E90" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G90" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L90" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="91" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A91" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D91" s="6" t="str">
+    </row>
+    <row r="92" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A92" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D92" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E92" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G92" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L92" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E91" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G91" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L91" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="92" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D92" s="6" t="str">
+    </row>
+    <row r="93" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A93" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D93" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E93" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G93" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L93" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E92" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G92" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L92" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="93" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D93" s="6" t="str">
+    </row>
+    <row r="94" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A94" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D94" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E94" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G94" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L94" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E93" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G93" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L93" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="94" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A94" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D94" s="6" t="str">
+    </row>
+    <row r="95" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A95" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D95" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E95" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G95" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L95" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E94" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G94" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L94" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="95" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A95" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D95" s="6" t="str">
+    </row>
+    <row r="96" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A96" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D96" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E96" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G96" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L96" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E95" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G95" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L95" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="96" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A96" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D96" s="6" t="str">
+    </row>
+    <row r="97" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A97" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D97" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E97" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G97" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L97" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E96" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G96" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L96" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="97" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A97" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D97" s="6" t="str">
+    </row>
+    <row r="98" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A98" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D98" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E98" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G98" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L98" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E97" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G97" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L97" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="98" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A98" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D98" s="6" t="str">
+    </row>
+    <row r="99" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A99" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D99" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E99" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G99" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L99" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E98" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G98" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L98" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="99" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A99" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D99" s="6" t="str">
+    </row>
+    <row r="100" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A100" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D100" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E100" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G100" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L100" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E99" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G99" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L99" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="100" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A100" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D100" s="6" t="str">
+    </row>
+    <row r="101" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A101" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D101" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E101" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G101" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L101" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E100" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G100" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L100" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="101" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A101" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D101" s="6" t="str">
+    </row>
+    <row r="102" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A102" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D102" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E102" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G102" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L102" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E101" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G101" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L101" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="102" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A102" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D102" s="6" t="str">
+    </row>
+    <row r="103" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A103" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D103" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E103" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G103" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L103" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E102" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G102" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L102" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="103" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A103" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D103" s="6" t="str">
+    </row>
+    <row r="104" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A104" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D104" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E104" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G104" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L104" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E103" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G103" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L103" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="104" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A104" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D104" s="6" t="str">
+    </row>
+    <row r="105" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A105" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D105" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E105" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G105" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L105" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E104" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G104" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L104" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="105" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D105" s="6" t="str">
+    </row>
+    <row r="106" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A106" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D106" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E106" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G106" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L106" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E105" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G105" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L105" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="106" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A106" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D106" s="6" t="str">
+    </row>
+    <row r="107" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A107" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D107" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E107" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G107" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L107" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E106" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G106" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L106" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="107" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A107" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D107" s="6" t="str">
+    </row>
+    <row r="108" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A108" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D108" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E108" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G108" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L108" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E107" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G107" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L107" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="108" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A108" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D108" s="6" t="str">
+    </row>
+    <row r="109" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A109" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D109" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E109" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G109" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L109" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E108" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G108" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L108" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="109" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A109" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D109" s="6" t="str">
+    </row>
+    <row r="110" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A110" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D110" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E110" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G110" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L110" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E109" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G109" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L109" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="110" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A110" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D110" s="6" t="str">
+    </row>
+    <row r="111" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A111" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D111" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E111" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G111" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L111" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E110" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G110" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L110" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="111" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A111" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D111" s="6" t="str">
+    </row>
+    <row r="112" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A112" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D112" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E112" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G112" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L112" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="E111" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G111" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L111" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="112" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A112" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D112" s="6" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="E112" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G112" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L112" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="113" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A113" s="51" t="str">
         <f t="shared" ref="A113:A170" si="8">IF(B113="","",IF(D113=D112,A112+1,(D113*100)))</f>
         <v/>
       </c>
       <c r="D113" s="6" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="E113" s="50" t="str">
@@ -3875,13 +3901,13 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A114" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D114" s="6" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="E114" s="50" t="str">
@@ -3897,13 +3923,13 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A115" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D115" s="6" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="E115" s="50" t="str">
@@ -3919,13 +3945,13 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A116" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D116" s="6" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="E116" s="50" t="str">
@@ -3941,13 +3967,13 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A117" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D117" s="6" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="E117" s="50" t="str">
@@ -3963,13 +3989,13 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A118" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D118" s="6" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="E118" s="50" t="str">
@@ -3985,13 +4011,13 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A119" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D119" s="6" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="E119" s="50" t="str">
@@ -4007,13 +4033,13 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A120" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D120" s="6" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="E120" s="50" t="str">
@@ -4029,13 +4055,13 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A121" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D121" s="6" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="E121" s="50" t="str">
@@ -4051,13 +4077,13 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A122" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D122" s="6" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="E122" s="50" t="str">
@@ -4073,13 +4099,13 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A123" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D123" s="6" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="E123" s="50" t="str">
@@ -4095,13 +4121,13 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A124" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D124" s="6" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="E124" s="50" t="str">
@@ -4117,7 +4143,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A125" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4139,7 +4165,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A126" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4161,7 +4187,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A127" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4183,7 +4209,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A128" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4205,7 +4231,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A129" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4227,7 +4253,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A130" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4249,7 +4275,7 @@
         <v/>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A131" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4271,7 +4297,7 @@
         <v/>
       </c>
     </row>
-    <row r="132" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A132" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4293,7 +4319,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A133" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4315,7 +4341,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A134" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4337,7 +4363,7 @@
         <v/>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A135" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4359,7 +4385,7 @@
         <v/>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A136" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4381,7 +4407,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A137" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4403,7 +4429,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A138" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4425,7 +4451,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A139" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4447,7 +4473,7 @@
         <v/>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A140" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4469,7 +4495,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A141" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4491,7 +4517,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A142" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4513,7 +4539,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A143" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4535,7 +4561,7 @@
         <v/>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A144" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4557,7 +4583,7 @@
         <v/>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A145" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4579,7 +4605,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A146" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4601,7 +4627,7 @@
         <v/>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A147" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4623,7 +4649,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A148" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4645,7 +4671,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A149" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4667,7 +4693,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A150" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4689,7 +4715,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A151" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4711,7 +4737,7 @@
         <v/>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A152" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4733,7 +4759,7 @@
         <v/>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A153" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4755,7 +4781,7 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A154" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4777,7 +4803,7 @@
         <v/>
       </c>
     </row>
-    <row r="155" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A155" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4799,7 +4825,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A156" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4821,7 +4847,7 @@
         <v/>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A157" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4843,7 +4869,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A158" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4865,7 +4891,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A159" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4887,7 +4913,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A160" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4909,7 +4935,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A161" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4931,7 +4957,7 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A162" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4953,7 +4979,7 @@
         <v/>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A163" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4975,7 +5001,7 @@
         <v/>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A164" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4997,7 +5023,7 @@
         <v/>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A165" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5019,7 +5045,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A166" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5041,7 +5067,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A167" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5063,7 +5089,7 @@
         <v/>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A168" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5085,7 +5111,7 @@
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A169" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5107,7 +5133,7 @@
         <v/>
       </c>
     </row>
-    <row r="170" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A170" s="51" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5131,6 +5157,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="H9:K9"/>
     <mergeCell ref="J10:J11"/>
     <mergeCell ref="M35:M39"/>
     <mergeCell ref="A1:B1"/>
@@ -5147,7 +5174,6 @@
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="M9:M11"/>
     <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H9:K9"/>
   </mergeCells>
   <conditionalFormatting sqref="G14:G170">
     <cfRule type="colorScale" priority="2">

--- a/project requirements spreadsheet.xlsx
+++ b/project requirements spreadsheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Documents\__ School\CS 3300- Software Development\Project (Group 1)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A672E39-7DA6-419F-82F0-222F3B7CB667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87EF1400-D4A3-45A4-BD64-26CEC52F5C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15960" xr2:uid="{CAB5D44A-E176-404C-B398-BEAD2D9E6884}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="96">
   <si>
     <t>Intro to Software Engineering</t>
   </si>
@@ -420,7 +420,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -460,12 +460,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC5C5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,7 +580,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -792,32 +786,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1193,7 +1166,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B900A37F-814E-4AF4-9047-E946E2A67EEB}">
-  <dimension ref="A1:M169"/>
+  <dimension ref="A1:M168"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" style="6" customWidth="1"/>
@@ -1210,51 +1183,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="73" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="81"/>
+      <c r="B1" s="74"/>
       <c r="C1" s="29"/>
-      <c r="D1" s="86" t="s">
+      <c r="D1" s="79" t="s">
         <v>91</v>
       </c>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="86"/>
-      <c r="J1" s="86"/>
-      <c r="K1" s="86"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
       <c r="L1" s="29"/>
       <c r="M1" s="31"/>
     </row>
     <row r="2" spans="1:13" s="32" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="82" t="s">
+      <c r="A2" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="83"/>
+      <c r="B2" s="76"/>
       <c r="C2" s="29"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="86"/>
-      <c r="J2" s="86"/>
-      <c r="K2" s="86"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="52"/>
       <c r="B3" s="39"/>
       <c r="C3" s="13"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="79"/>
       <c r="L3" s="13"/>
       <c r="M3" s="13"/>
     </row>
@@ -1265,14 +1238,14 @@
       <c r="B4" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="79"/>
+      <c r="K4" s="79"/>
     </row>
     <row r="5" spans="1:13" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="53" t="s">
@@ -1281,14 +1254,14 @@
       <c r="B5" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="86"/>
-      <c r="E5" s="86"/>
-      <c r="F5" s="86"/>
-      <c r="G5" s="86"/>
-      <c r="H5" s="86"/>
-      <c r="I5" s="86"/>
-      <c r="J5" s="86"/>
-      <c r="K5" s="86"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
+      <c r="K5" s="79"/>
     </row>
     <row r="6" spans="1:13" s="7" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="54" t="s">
@@ -1297,14 +1270,14 @@
       <c r="B6" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="D6" s="86"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="86"/>
-      <c r="H6" s="86"/>
-      <c r="I6" s="86"/>
-      <c r="J6" s="86"/>
-      <c r="K6" s="86"/>
+      <c r="D6" s="79"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
+      <c r="J6" s="79"/>
+      <c r="K6" s="79"/>
       <c r="L6" s="1"/>
       <c r="M6" s="33"/>
     </row>
@@ -1324,73 +1297,73 @@
       <c r="M7" s="33"/>
     </row>
     <row r="8" spans="1:13" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="76" t="s">
+      <c r="A8" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="76"/>
-      <c r="C8" s="76"/>
-      <c r="D8" s="76"/>
-      <c r="E8" s="76"/>
-      <c r="F8" s="76"/>
-      <c r="G8" s="76"/>
-      <c r="H8" s="76"/>
-      <c r="I8" s="76"/>
-      <c r="J8" s="76"/>
-      <c r="K8" s="76"/>
-      <c r="L8" s="76"/>
-      <c r="M8" s="76"/>
+      <c r="B8" s="70"/>
+      <c r="C8" s="70"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="70"/>
+      <c r="K8" s="70"/>
+      <c r="L8" s="70"/>
+      <c r="M8" s="70"/>
     </row>
     <row r="9" spans="1:13" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="76" t="s">
+      <c r="C9" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="76"/>
-      <c r="E9" s="76"/>
-      <c r="F9" s="76"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="76" t="s">
+      <c r="H9" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="76"/>
-      <c r="J9" s="76"/>
-      <c r="K9" s="76"/>
-      <c r="L9" s="87" t="s">
+      <c r="I9" s="70"/>
+      <c r="J9" s="70"/>
+      <c r="K9" s="70"/>
+      <c r="L9" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="M9" s="88" t="s">
+      <c r="M9" s="81" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:13" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="77" t="s">
+      <c r="C10" s="69" t="s">
         <v>21</v>
       </c>
       <c r="D10" s="1"/>
-      <c r="E10" s="77" t="s">
+      <c r="E10" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="77" t="s">
+      <c r="F10" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="77" t="s">
+      <c r="G10" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="H10" s="77" t="s">
+      <c r="H10" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="I10" s="77" t="s">
+      <c r="I10" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="77" t="s">
+      <c r="J10" s="69" t="s">
         <v>5</v>
       </c>
       <c r="K10" s="1"/>
-      <c r="L10" s="87"/>
-      <c r="M10" s="88"/>
+      <c r="L10" s="80"/>
+      <c r="M10" s="81"/>
     </row>
     <row r="11" spans="1:13" s="7" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
@@ -1399,24 +1372,24 @@
       <c r="B11" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="77"/>
+      <c r="C11" s="69"/>
       <c r="D11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="77"/>
-      <c r="J11" s="77"/>
+      <c r="E11" s="69"/>
+      <c r="F11" s="69"/>
+      <c r="G11" s="69"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="69"/>
+      <c r="J11" s="69"/>
       <c r="K11" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="L11" s="87"/>
-      <c r="M11" s="88"/>
+      <c r="L11" s="80"/>
+      <c r="M11" s="81"/>
     </row>
     <row r="12" spans="1:13" s="68" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="84" t="s">
+      <c r="A12" s="77" t="s">
         <v>40</v>
       </c>
       <c r="B12" s="63"/>
@@ -1443,7 +1416,7 @@
       <c r="M12" s="67"/>
     </row>
     <row r="13" spans="1:13" s="3" customFormat="1" ht="61.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="85"/>
+      <c r="A13" s="78"/>
       <c r="B13" s="8"/>
       <c r="C13" s="10"/>
       <c r="D13" s="10" t="s">
@@ -2035,7 +2008,7 @@
         <v>-20</v>
       </c>
       <c r="L35" s="12"/>
-      <c r="M35" s="78" t="s">
+      <c r="M35" s="71" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2064,7 +2037,7 @@
         <v>-20</v>
       </c>
       <c r="L36" s="12"/>
-      <c r="M36" s="79"/>
+      <c r="M36" s="72"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="60">
@@ -2091,7 +2064,7 @@
         <v>-20</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="M37" s="79"/>
+      <c r="M37" s="72"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="60">
@@ -2118,7 +2091,7 @@
         <v>-20</v>
       </c>
       <c r="L38" s="12"/>
-      <c r="M38" s="79"/>
+      <c r="M38" s="72"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="60">
@@ -2145,7 +2118,7 @@
         <v>-20</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="79"/>
+      <c r="M39" s="72"/>
     </row>
     <row r="40" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="60">
@@ -2383,46 +2356,42 @@
       <c r="K47" s="18"/>
       <c r="L47" s="22"/>
     </row>
-    <row r="48" spans="1:13" s="75" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="69">
-        <f>IF(B48="","",IF(D48=D47,A47+1,(D48*100)))</f>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="51">
+        <f t="shared" ref="A48:A110" si="3">IF(B48="","",IF(D48=D47,A47+1,(D48*100)))</f>
         <v>101</v>
       </c>
-      <c r="B48" s="70" t="str">
-        <f>"Iteration "&amp;D48-1&amp;" Test Report (Optional)"</f>
-        <v>Iteration 0 Test Report (Optional)</v>
-      </c>
-      <c r="C48" s="71" t="s">
+      <c r="B48" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D48" s="71">
+      <c r="D48" s="6">
         <v>1</v>
       </c>
-      <c r="E48" s="72">
-        <v>45596</v>
-      </c>
-      <c r="F48" s="73"/>
-      <c r="G48" s="71">
-        <f>IF(B48="","",IF(AND(E48&gt;0,F48&gt;0),F48-E48,0))</f>
+      <c r="E48" s="12">
+        <v>45638</v>
+      </c>
+      <c r="G48" s="6">
+        <f t="shared" ref="G48:G110" si="4">IF(B48="","",IF(AND(E48&gt;0,F48&gt;0),F48-E48,0))</f>
         <v>0</v>
       </c>
-      <c r="H48" s="71"/>
-      <c r="I48" s="71"/>
-      <c r="J48" s="71"/>
-      <c r="K48" s="71"/>
-      <c r="L48" s="72"/>
-      <c r="M48" s="74"/>
+      <c r="H48" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="L48" s="12"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="60">
-        <f t="shared" ref="A49:A111" si="3">IF(B49="","",IF(D49=D48,A48+1,(D49*100)))</f>
+        <f t="shared" si="3"/>
         <v>102</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D49" s="6">
         <v>1</v>
@@ -2430,9 +2399,12 @@
       <c r="E49" s="12">
         <v>45638</v>
       </c>
+      <c r="F49" s="12">
+        <v>45593</v>
+      </c>
       <c r="G49" s="6">
-        <f t="shared" ref="G49:G111" si="4">IF(B49="","",IF(AND(E49&gt;0,F49&gt;0),F49-E49,0))</f>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>-45</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>46</v>
@@ -2445,25 +2417,29 @@
         <v>103</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D50" s="6">
         <v>1</v>
       </c>
       <c r="E50" s="12">
-        <v>45638</v>
+        <v>45596</v>
+      </c>
+      <c r="F50" s="12">
+        <f>F45</f>
+        <v>45562</v>
       </c>
       <c r="G50" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>46</v>
+        <v>-34</v>
       </c>
       <c r="L50" s="12"/>
+      <c r="M50" s="25" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="60">
@@ -2471,10 +2447,10 @@
         <v>104</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D51" s="6">
         <v>1</v>
@@ -2482,14 +2458,14 @@
       <c r="E51" s="12">
         <v>45596</v>
       </c>
+      <c r="F51" s="12">
+        <v>45592</v>
+      </c>
       <c r="G51" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L51" s="12"/>
-      <c r="M51" s="25" t="s">
-        <v>62</v>
-      </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="60">
@@ -2497,10 +2473,10 @@
         <v>105</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D52" s="6">
         <v>1</v>
@@ -2509,113 +2485,114 @@
         <v>45596</v>
       </c>
       <c r="F52" s="12">
-        <v>45592</v>
+        <v>45595</v>
       </c>
       <c r="G52" s="6">
         <f t="shared" si="4"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="L52" s="12"/>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" s="15" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="60">
         <f t="shared" si="3"/>
         <v>106</v>
       </c>
-      <c r="B53" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C53" s="6" t="s">
+      <c r="B53" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D53" s="10">
+        <v>1</v>
+      </c>
+      <c r="E53" s="14">
+        <v>45596</v>
+      </c>
+      <c r="F53" s="10"/>
+      <c r="G53" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H53" s="10"/>
+      <c r="I53" s="10"/>
+      <c r="J53" s="10"/>
+      <c r="K53" s="10"/>
+      <c r="L53" s="14"/>
+      <c r="M53" s="26"/>
+    </row>
+    <row r="54" spans="1:13" s="16" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="51">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+      <c r="B54" s="2" t="str">
+        <f>"Iteration " &amp; D54 &amp; " Completion"</f>
+        <v>Iteration 2 Completion</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D54" s="1">
+        <v>2</v>
+      </c>
+      <c r="E54" s="50">
+        <v>45601</v>
+      </c>
+      <c r="F54" s="1"/>
+      <c r="G54" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="12"/>
+      <c r="M54" s="34"/>
+    </row>
+    <row r="55" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="51">
+        <f t="shared" si="3"/>
+        <v>201</v>
+      </c>
+      <c r="B55" s="5" t="str">
+        <f>"Iteration "&amp;D55-1&amp;" Test Report"</f>
+        <v>Iteration 1 Test Report</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D55" s="6">
+        <v>2</v>
+      </c>
+      <c r="E55" s="50">
+        <f t="shared" ref="E55:E118" si="5">IF(B55="","",IF(D55=D54,E54,E54+14))</f>
+        <v>45601</v>
+      </c>
+      <c r="G55" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L55" s="12"/>
+    </row>
+    <row r="56" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A56" s="51">
+        <f t="shared" si="3"/>
+        <v>202</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C56" s="6" t="s">
         <v>42</v>
-      </c>
-      <c r="D53" s="6">
-        <v>1</v>
-      </c>
-      <c r="E53" s="12">
-        <v>45596</v>
-      </c>
-      <c r="G53" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L53" s="12"/>
-    </row>
-    <row r="54" spans="1:13" s="15" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="60">
-        <f t="shared" si="3"/>
-        <v>107</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C54" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D54" s="10">
-        <v>1</v>
-      </c>
-      <c r="E54" s="14">
-        <v>45596</v>
-      </c>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H54" s="10"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="14"/>
-      <c r="M54" s="26"/>
-    </row>
-    <row r="55" spans="1:13" s="16" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="51">
-        <f t="shared" si="3"/>
-        <v>200</v>
-      </c>
-      <c r="B55" s="2" t="str">
-        <f>"Iteration " &amp; D55 &amp; " Completion"</f>
-        <v>Iteration 2 Completion</v>
-      </c>
-      <c r="C55" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D55" s="1">
-        <v>2</v>
-      </c>
-      <c r="E55" s="50">
-        <v>45601</v>
-      </c>
-      <c r="F55" s="1"/>
-      <c r="G55" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
-      <c r="L55" s="12"/>
-      <c r="M55" s="34"/>
-    </row>
-    <row r="56" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="51">
-        <f t="shared" si="3"/>
-        <v>201</v>
-      </c>
-      <c r="B56" s="5" t="str">
-        <f>"Iteration "&amp;D56-1&amp;" Test Report"</f>
-        <v>Iteration 1 Test Report</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>45</v>
       </c>
       <c r="D56" s="6">
         <v>2</v>
       </c>
       <c r="E56" s="50">
-        <f t="shared" ref="E56:E119" si="5">IF(B56="","",IF(D56=D55,E55,E55+14))</f>
+        <f t="shared" si="5"/>
         <v>45601</v>
       </c>
       <c r="G56" s="6">
@@ -2627,13 +2604,13 @@
     <row r="57" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="51">
         <f t="shared" si="3"/>
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D57" s="6">
         <v>2</v>
@@ -2651,15 +2628,16 @@
     <row r="58" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="51">
         <f t="shared" si="3"/>
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>44</v>
       </c>
       <c r="D58" s="6">
+        <f>IF(B58="","",D57)</f>
         <v>2</v>
       </c>
       <c r="E58" s="50">
@@ -2675,16 +2653,16 @@
     <row r="59" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="51">
         <f t="shared" si="3"/>
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D59" s="6">
-        <f>IF(B59="","",D58)</f>
+        <f t="shared" ref="D59:D122" si="6">IF(B59="","",D58)</f>
         <v>2</v>
       </c>
       <c r="E59" s="50">
@@ -2700,16 +2678,16 @@
     <row r="60" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="51">
         <f t="shared" si="3"/>
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D60" s="6">
-        <f t="shared" ref="D60:D123" si="6">IF(B60="","",D59)</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="E60" s="50">
@@ -2720,34 +2698,31 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L60" s="12"/>
+      <c r="L60" s="12">
+        <f t="shared" ref="L60:L110" si="7">IF(B60="","",IF(D60=D59,L59,IF(F60&gt;0,F60,"Not Delivered")))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="61" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="51">
-        <f t="shared" si="3"/>
-        <v>206</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D61" s="6">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="E61" s="50">
-        <f t="shared" si="5"/>
-        <v>45601</v>
-      </c>
-      <c r="G61" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L61" s="12">
-        <f t="shared" ref="L61:L111" si="7">IF(B61="","",IF(D61=D60,L60,IF(F61&gt;0,F61,"Not Delivered")))</f>
-        <v>0</v>
+      <c r="A61" s="51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D61" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E61" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G61" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L61" s="12" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
     </row>
     <row r="62" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -3830,7 +3805,7 @@
     </row>
     <row r="111" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="51" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="A111:A168" si="8">IF(B111="","",IF(D111=D110,A110+1,(D111*100)))</f>
         <v/>
       </c>
       <c r="D111" s="6" t="str">
@@ -3842,17 +3817,17 @@
         <v/>
       </c>
       <c r="G111" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="G111:G168" si="9">IF(B111="","",IF(AND(E111&gt;0,F111&gt;0),F111-E111,0))</f>
         <v/>
       </c>
       <c r="L111" s="12" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="L111:L168" si="10">IF(B111="","",IF(D111=D110,L110,IF(F111&gt;0,F111,"Not Delivered")))</f>
         <v/>
       </c>
     </row>
     <row r="112" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="51" t="str">
-        <f t="shared" ref="A112:A169" si="8">IF(B112="","",IF(D112=D111,A111+1,(D112*100)))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="D112" s="6" t="str">
@@ -3864,11 +3839,11 @@
         <v/>
       </c>
       <c r="G112" s="6" t="str">
-        <f t="shared" ref="G112:G169" si="9">IF(B112="","",IF(AND(E112&gt;0,F112&gt;0),F112-E112,0))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="L112" s="12" t="str">
-        <f t="shared" ref="L112:L169" si="10">IF(B112="","",IF(D112=D111,L111,IF(F112&gt;0,F112,"Not Delivered")))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -4014,7 +3989,7 @@
         <v/>
       </c>
       <c r="E119" s="50" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="E119:E168" si="11">IF(B119="","",IF(D119=D118,E118,E118+14))</f>
         <v/>
       </c>
       <c r="G119" s="6" t="str">
@@ -4036,7 +4011,7 @@
         <v/>
       </c>
       <c r="E120" s="50" t="str">
-        <f t="shared" ref="E120:E169" si="11">IF(B120="","",IF(D120=D119,E119,E119+14))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G120" s="6" t="str">
@@ -4098,7 +4073,7 @@
         <v/>
       </c>
       <c r="D123" s="6" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="D123:D168" si="12">IF(B123="","",D122)</f>
         <v/>
       </c>
       <c r="E123" s="50" t="str">
@@ -4120,7 +4095,7 @@
         <v/>
       </c>
       <c r="D124" s="6" t="str">
-        <f t="shared" ref="D124:D169" si="12">IF(B124="","",D123)</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="E124" s="50" t="str">
@@ -5104,30 +5079,9 @@
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A169" s="51" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="D169" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E169" s="50" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G169" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="L169" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="M9:M11"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H9:K9"/>
     <mergeCell ref="J10:J11"/>
@@ -5144,10 +5098,9 @@
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="F10:F11"/>
-    <mergeCell ref="M9:M11"/>
   </mergeCells>
-  <conditionalFormatting sqref="G14:G169">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="G14:G168">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/project requirements spreadsheet.xlsx
+++ b/project requirements spreadsheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Documents\__ School\CS 3300- Software Development\Project (Group 1)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E66C24B-5F65-471F-BFA0-520C91FCFA3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A7E8C2-17B6-4E91-97FB-CC910C5F07BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{CAB5D44A-E176-404C-B398-BEAD2D9E6884}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" xr2:uid="{CAB5D44A-E176-404C-B398-BEAD2D9E6884}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="118">
   <si>
     <t>Intro to Software Engineering</t>
   </si>
@@ -334,7 +334,70 @@
     <t>Add to the puzzle description reason puzzle is being solved</t>
   </si>
   <si>
+    <t>A, I</t>
+  </si>
+  <si>
+    <t>A,I</t>
+  </si>
+  <si>
+    <t>T,I</t>
+  </si>
+  <si>
+    <t>T, A, I</t>
+  </si>
+  <si>
+    <t>T,A,I</t>
+  </si>
+  <si>
+    <t>T,O</t>
+  </si>
+  <si>
+    <t>T,A,I,O</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>T, I,O</t>
+  </si>
+  <si>
+    <t>IT-1.07</t>
+  </si>
+  <si>
+    <t>Iteration 1.0 Test Report</t>
+  </si>
+  <si>
     <t>There was a slight delay with testing caused by GIT management issues on Dev side. Puzzle and Dev branches not properly merged, Taylor had to fix and re-push Sunday (11/3)</t>
+  </si>
+  <si>
+    <t>Fix Core Game Bugs from Test Report</t>
+  </si>
+  <si>
+    <t>Fix Puzzle Bugs from Test Report</t>
+  </si>
+  <si>
+    <t>Map handles Room Generation not Individual Rooms (To prevent duplicate rooms issues)</t>
+  </si>
+  <si>
+    <t>key item ends game properly</t>
+  </si>
+  <si>
+    <t>Generate Gameplay Test Document</t>
+  </si>
+  <si>
+    <t>S Welton / J Hong</t>
+  </si>
+  <si>
+    <t>Add Reset Counter to Start() methods for puzzles</t>
+  </si>
+  <si>
+    <t>*(If time) Break Puzzles into Clue Items so passwords arent provided with puzzle</t>
+  </si>
+  <si>
+    <t>*(If Time) Doors locking.unliocking</t>
+  </si>
+  <si>
+    <t>Start Dev Document</t>
   </si>
 </sst>
 </file>
@@ -345,7 +408,7 @@
     <numFmt numFmtId="164" formatCode="&quot;IT-&quot;0&quot;.&quot;00"/>
     <numFmt numFmtId="165" formatCode="&quot;Class&quot;00"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -422,6 +485,11 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -467,7 +535,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -579,11 +647,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -630,9 +707,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -789,44 +863,74 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1169,123 +1273,123 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B900A37F-814E-4AF4-9047-E946E2A67EEB}">
-  <dimension ref="A1:M168"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M169"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.5703125" style="6" customWidth="1"/>
-    <col min="2" max="2" width="61.28515625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="6" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.7109375" style="6" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" style="6" customWidth="1"/>
-    <col min="9" max="11" width="12.7109375" style="6" customWidth="1"/>
-    <col min="12" max="12" width="16.42578125" style="6" customWidth="1"/>
-    <col min="13" max="13" width="173.85546875" style="25" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="13"/>
+    <col min="1" max="1" width="15.44140625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="61.33203125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.6640625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" style="6" customWidth="1"/>
+    <col min="9" max="11" width="12.6640625" style="6" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" style="6" customWidth="1"/>
+    <col min="13" max="13" width="173.77734375" style="24" customWidth="1"/>
+    <col min="14" max="16384" width="9.109375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+    <row r="1" spans="1:13" s="31" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="80" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="80" t="s">
+      <c r="B1" s="81"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="87" t="s">
         <v>91</v>
       </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="31"/>
-    </row>
-    <row r="2" spans="1:13" s="32" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="77"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="52"/>
-      <c r="B3" s="39"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
+      <c r="J1" s="87"/>
+      <c r="K1" s="87"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="30"/>
+    </row>
+    <row r="2" spans="1:13" s="31" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="83"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
+      <c r="I2" s="87"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="87"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="51"/>
+      <c r="B3" s="38"/>
       <c r="C3" s="13"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="80"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
+      <c r="I3" s="87"/>
+      <c r="J3" s="87"/>
+      <c r="K3" s="87"/>
       <c r="L3" s="13"/>
       <c r="M3" s="13"/>
     </row>
-    <row r="4" spans="1:13" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="53" t="s">
+    <row r="4" spans="1:13" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="80"/>
-      <c r="K4" s="80"/>
-    </row>
-    <row r="5" spans="1:13" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="53" t="s">
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
+    </row>
+    <row r="5" spans="1:13" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80"/>
-    </row>
-    <row r="6" spans="1:13" s="7" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="54" t="s">
+      <c r="D5" s="87"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87"/>
+      <c r="H5" s="87"/>
+      <c r="I5" s="87"/>
+      <c r="J5" s="87"/>
+      <c r="K5" s="87"/>
+    </row>
+    <row r="6" spans="1:13" s="7" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="D6" s="80"/>
-      <c r="E6" s="80"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="80"/>
-      <c r="K6" s="80"/>
+      <c r="D6" s="87"/>
+      <c r="E6" s="87"/>
+      <c r="F6" s="87"/>
+      <c r="G6" s="87"/>
+      <c r="H6" s="87"/>
+      <c r="I6" s="87"/>
+      <c r="J6" s="87"/>
+      <c r="K6" s="87"/>
       <c r="L6" s="1"/>
-      <c r="M6" s="33"/>
-    </row>
-    <row r="7" spans="1:13" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="55"/>
+      <c r="M6" s="32"/>
+    </row>
+    <row r="7" spans="1:13" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="54"/>
       <c r="B7" s="2"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -1297,182 +1401,182 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
-      <c r="M7" s="33"/>
-    </row>
-    <row r="8" spans="1:13" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="71" t="s">
+      <c r="M7" s="32"/>
+    </row>
+    <row r="8" spans="1:13" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="71"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="71"/>
-      <c r="K8" s="71"/>
-      <c r="L8" s="71"/>
-      <c r="M8" s="71"/>
-    </row>
-    <row r="9" spans="1:13" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="88"/>
+      <c r="C8" s="88"/>
+      <c r="D8" s="88"/>
+      <c r="E8" s="88"/>
+      <c r="F8" s="88"/>
+      <c r="G8" s="88"/>
+      <c r="H8" s="88"/>
+      <c r="I8" s="88"/>
+      <c r="J8" s="88"/>
+      <c r="K8" s="88"/>
+      <c r="L8" s="88"/>
+      <c r="M8" s="88"/>
+    </row>
+    <row r="9" spans="1:13" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="71" t="s">
+      <c r="C9" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="71"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
+      <c r="D9" s="88"/>
+      <c r="E9" s="88"/>
+      <c r="F9" s="88"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="71" t="s">
+      <c r="H9" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="71"/>
-      <c r="J9" s="71"/>
-      <c r="K9" s="71"/>
-      <c r="L9" s="81" t="s">
+      <c r="I9" s="88"/>
+      <c r="J9" s="88"/>
+      <c r="K9" s="88"/>
+      <c r="L9" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="M9" s="69" t="s">
+      <c r="M9" s="90" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:13" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" s="7" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="70" t="s">
+      <c r="C10" s="86" t="s">
         <v>21</v>
       </c>
       <c r="D10" s="1"/>
-      <c r="E10" s="70" t="s">
+      <c r="E10" s="86" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="70" t="s">
+      <c r="F10" s="86" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="70" t="s">
+      <c r="G10" s="86" t="s">
         <v>60</v>
       </c>
-      <c r="H10" s="70" t="s">
+      <c r="H10" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="I10" s="70" t="s">
+      <c r="I10" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="70" t="s">
+      <c r="J10" s="86" t="s">
         <v>5</v>
       </c>
       <c r="K10" s="1"/>
-      <c r="L10" s="81"/>
-      <c r="M10" s="69"/>
-    </row>
-    <row r="11" spans="1:13" s="7" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L10" s="89"/>
+      <c r="M10" s="90"/>
+    </row>
+    <row r="11" spans="1:13" s="7" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="70"/>
+      <c r="C11" s="86"/>
       <c r="D11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="70"/>
-      <c r="K11" s="30" t="s">
+      <c r="E11" s="86"/>
+      <c r="F11" s="86"/>
+      <c r="G11" s="86"/>
+      <c r="H11" s="86"/>
+      <c r="I11" s="86"/>
+      <c r="J11" s="86"/>
+      <c r="K11" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="L11" s="81"/>
-      <c r="M11" s="69"/>
-    </row>
-    <row r="12" spans="1:13" s="68" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="78" t="s">
+      <c r="L11" s="89"/>
+      <c r="M11" s="90"/>
+    </row>
+    <row r="12" spans="1:13" s="67" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="84" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="63"/>
-      <c r="C12" s="21" t="s">
+      <c r="B12" s="62"/>
+      <c r="C12" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="21"/>
-      <c r="F12" s="64" t="s">
+      <c r="E12" s="20"/>
+      <c r="F12" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21" t="s">
+      <c r="G12" s="20"/>
+      <c r="H12" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="65"/>
-      <c r="J12" s="65"/>
-      <c r="K12" s="21" t="s">
+      <c r="I12" s="64"/>
+      <c r="J12" s="64"/>
+      <c r="K12" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="L12" s="66"/>
-      <c r="M12" s="67"/>
-    </row>
-    <row r="13" spans="1:13" s="3" customFormat="1" ht="61.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="79"/>
+      <c r="L12" s="65"/>
+      <c r="M12" s="66"/>
+    </row>
+    <row r="13" spans="1:13" s="3" customFormat="1" ht="61.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="85"/>
       <c r="B13" s="8"/>
       <c r="C13" s="10"/>
       <c r="D13" s="10" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="10"/>
-      <c r="F13" s="35" t="s">
+      <c r="F13" s="34" t="s">
         <v>12</v>
       </c>
       <c r="G13" s="10"/>
-      <c r="H13" s="27" t="s">
+      <c r="H13" s="26" t="s">
         <v>43</v>
       </c>
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
       <c r="K13" s="10"/>
       <c r="L13" s="11"/>
-      <c r="M13" s="36"/>
-    </row>
-    <row r="14" spans="1:13" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="56">
-        <v>0</v>
-      </c>
-      <c r="B14" s="20" t="s">
+      <c r="M13" s="35"/>
+    </row>
+    <row r="14" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="55">
+        <v>0</v>
+      </c>
+      <c r="B14" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="21" t="s">
+      <c r="D14" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="21">
         <v>45566</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="21">
         <v>45564</v>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="20">
         <f>IF(AND(E14&gt;0,F14&gt;0),F14-E14,"")</f>
         <v>-2</v>
       </c>
-      <c r="H14" s="21" t="s">
+      <c r="H14" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="24"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="57">
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="23"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="56">
         <f>A14+1</f>
         <v>1</v>
       </c>
@@ -1497,8 +1601,8 @@
       </c>
       <c r="L15" s="12"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="57">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" s="56">
         <f t="shared" ref="A16:A33" si="0">A15+1</f>
         <v>2</v>
       </c>
@@ -1523,8 +1627,8 @@
       </c>
       <c r="L16" s="12"/>
     </row>
-    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="57">
+    <row r="17" spans="1:12" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="56">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -1549,8 +1653,8 @@
       </c>
       <c r="L17" s="12"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="57">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="56">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1575,8 +1679,8 @@
       </c>
       <c r="L18" s="12"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="57">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="56">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1601,8 +1705,8 @@
       </c>
       <c r="L19" s="12"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="57">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="56">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -1627,8 +1731,8 @@
       </c>
       <c r="L20" s="12"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="57">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="56">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -1653,8 +1757,8 @@
       </c>
       <c r="L21" s="12"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="57">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="56">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1679,15 +1783,15 @@
       </c>
       <c r="L22" s="12"/>
     </row>
-    <row r="23" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="57">
+    <row r="23" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="56">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="27" t="s">
         <v>54</v>
       </c>
       <c r="D23" s="6" t="s">
@@ -1705,15 +1809,15 @@
       </c>
       <c r="L23" s="12"/>
     </row>
-    <row r="24" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="57">
+    <row r="24" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="56">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="27" t="s">
         <v>54</v>
       </c>
       <c r="D24" s="6" t="s">
@@ -1731,15 +1835,15 @@
       </c>
       <c r="L24" s="12"/>
     </row>
-    <row r="25" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="57">
+    <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="56">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="27" t="s">
         <v>54</v>
       </c>
       <c r="D25" s="6" t="s">
@@ -1757,8 +1861,8 @@
       </c>
       <c r="L25" s="12"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="57">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="56">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -1786,8 +1890,8 @@
       </c>
       <c r="L26" s="12"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="57">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="56">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -1807,10 +1911,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="H27" s="6" t="s">
+        <v>96</v>
+      </c>
       <c r="L27" s="12"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="57">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="56">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -1830,10 +1937,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="H28" s="6" t="s">
+        <v>97</v>
+      </c>
       <c r="L28" s="12"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="57">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="56">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -1853,10 +1963,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="H29" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="L29" s="12"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="57">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="56">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -1876,10 +1989,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="H30" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="L30" s="12"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="57">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="56">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -1899,10 +2015,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="H31" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="L31" s="12"/>
     </row>
-    <row r="32" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="57">
+    <row r="32" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="56">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -1922,10 +2041,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="H32" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="L32" s="12"/>
     </row>
-    <row r="33" spans="1:13" s="15" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="58">
+    <row r="33" spans="1:13" s="15" customFormat="1" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="57">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
@@ -1946,48 +2068,50 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H33" s="10"/>
+      <c r="H33" s="10" t="s">
+        <v>102</v>
+      </c>
       <c r="I33" s="10"/>
       <c r="J33" s="10"/>
       <c r="K33" s="10"/>
       <c r="L33" s="14"/>
-      <c r="M33" s="26"/>
-    </row>
-    <row r="34" spans="1:13" s="19" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="59">
+      <c r="M33" s="25"/>
+    </row>
+    <row r="34" spans="1:13" s="18" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="58">
         <f>IF(D34=D33,A33+1,(D34*100))</f>
         <v>0</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D34" s="18">
-        <v>0</v>
-      </c>
-      <c r="E34" s="37">
+      <c r="D34" s="17">
+        <v>0</v>
+      </c>
+      <c r="E34" s="36">
         <v>45573</v>
       </c>
-      <c r="F34" s="37">
+      <c r="F34" s="36">
         <v>45587</v>
       </c>
-      <c r="G34" s="21">
+      <c r="G34" s="20">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="18"/>
-      <c r="K34" s="18"/>
-      <c r="L34" s="22"/>
-      <c r="M34" s="38" t="s">
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="21"/>
+      <c r="M34" s="37" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="60">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35" s="59">
         <f t="shared" ref="A35:A45" si="2">IF(D35=D34,A34+1,(D35*100))</f>
         <v>1</v>
       </c>
@@ -2010,13 +2134,16 @@
         <f t="shared" si="1"/>
         <v>-20</v>
       </c>
+      <c r="H35" s="6" t="s">
+        <v>97</v>
+      </c>
       <c r="L35" s="12"/>
-      <c r="M35" s="72" t="s">
+      <c r="M35" s="78" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="60">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36" s="59">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
@@ -2039,11 +2166,14 @@
         <f t="shared" si="1"/>
         <v>-20</v>
       </c>
+      <c r="H36" s="6" t="s">
+        <v>97</v>
+      </c>
       <c r="L36" s="12"/>
-      <c r="M36" s="73"/>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" s="60">
+      <c r="M36" s="79"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A37" s="59">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
@@ -2066,11 +2196,14 @@
         <f t="shared" si="1"/>
         <v>-20</v>
       </c>
+      <c r="H37" s="6" t="s">
+        <v>97</v>
+      </c>
       <c r="L37" s="12"/>
-      <c r="M37" s="73"/>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" s="60">
+      <c r="M37" s="79"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A38" s="59">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
@@ -2093,11 +2226,14 @@
         <f t="shared" si="1"/>
         <v>-20</v>
       </c>
+      <c r="H38" s="6" t="s">
+        <v>97</v>
+      </c>
       <c r="L38" s="12"/>
-      <c r="M38" s="73"/>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" s="60">
+      <c r="M38" s="79"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39" s="59">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
@@ -2120,11 +2256,14 @@
         <f t="shared" si="1"/>
         <v>-20</v>
       </c>
+      <c r="H39" s="6" t="s">
+        <v>97</v>
+      </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="73"/>
-    </row>
-    <row r="40" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="60">
+      <c r="M39" s="79"/>
+    </row>
+    <row r="40" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="59">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
@@ -2147,13 +2286,16 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
+      <c r="H40" s="6" t="s">
+        <v>97</v>
+      </c>
       <c r="L40" s="12"/>
-      <c r="M40" s="43" t="s">
+      <c r="M40" s="42" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="60">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41" s="59">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
@@ -2176,13 +2318,16 @@
         <f t="shared" si="1"/>
         <v>-9</v>
       </c>
+      <c r="H41" s="6" t="s">
+        <v>103</v>
+      </c>
       <c r="L41" s="12"/>
-      <c r="M41" s="43" t="s">
+      <c r="M41" s="42" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A42" s="60">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A42" s="59">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
@@ -2205,20 +2350,23 @@
         <f t="shared" si="1"/>
         <v>-9</v>
       </c>
+      <c r="H42" s="6" t="s">
+        <v>103</v>
+      </c>
       <c r="L42" s="12"/>
-      <c r="M42" s="25" t="s">
+      <c r="M42" s="24" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="60">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A43" s="59">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C43" s="42" t="s">
+      <c r="C43" s="41" t="s">
         <v>44</v>
       </c>
       <c r="D43" s="6">
@@ -2234,13 +2382,16 @@
         <f t="shared" si="1"/>
         <v>-9</v>
       </c>
+      <c r="H43" s="6" t="s">
+        <v>97</v>
+      </c>
       <c r="L43" s="12"/>
-      <c r="M43" s="34" t="s">
+      <c r="M43" s="33" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" s="60">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A44" s="59">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
@@ -2263,13 +2414,16 @@
         <f t="shared" si="1"/>
         <v>-11</v>
       </c>
+      <c r="H44" s="6" t="s">
+        <v>97</v>
+      </c>
       <c r="L44" s="12"/>
-      <c r="M44" s="25" t="s">
+      <c r="M44" s="24" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="45" spans="1:13" s="15" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="61">
+    <row r="45" spans="1:13" s="15" customFormat="1" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="60">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
@@ -2292,76 +2446,78 @@
         <f t="shared" si="1"/>
         <v>-11</v>
       </c>
-      <c r="H45" s="10"/>
+      <c r="H45" s="10" t="s">
+        <v>97</v>
+      </c>
       <c r="I45" s="10"/>
       <c r="J45" s="10"/>
       <c r="K45" s="10"/>
       <c r="L45" s="14"/>
-      <c r="M45" s="26" t="s">
+      <c r="M45" s="25" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="46" spans="1:13" s="49" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="62">
+    <row r="46" spans="1:13" s="48" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="61">
         <f>IF(D46=D44,A44+1,(D46*100))</f>
         <v>100</v>
       </c>
-      <c r="B46" s="44" t="s">
+      <c r="B46" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="C46" s="18" t="s">
+      <c r="C46" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D46" s="45">
+      <c r="D46" s="44">
         <v>1</v>
       </c>
-      <c r="E46" s="46">
+      <c r="E46" s="45">
         <v>45579</v>
       </c>
-      <c r="F46" s="47" t="s">
+      <c r="F46" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="G46" s="48"/>
-      <c r="H46" s="45"/>
-      <c r="I46" s="45"/>
-      <c r="J46" s="45"/>
-      <c r="K46" s="45"/>
-      <c r="L46" s="46"/>
-      <c r="M46" s="49" t="s">
+      <c r="G46" s="47"/>
+      <c r="H46" s="44"/>
+      <c r="I46" s="44"/>
+      <c r="J46" s="44"/>
+      <c r="K46" s="44"/>
+      <c r="L46" s="45"/>
+      <c r="M46" s="48" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="47" spans="1:13" s="19" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="59">
+    <row r="47" spans="1:13" s="18" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="58">
         <f>IF(D47=D45,A45+1,(D47*100))</f>
         <v>100</v>
       </c>
-      <c r="B47" s="17" t="s">
+      <c r="B47" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C47" s="18" t="s">
+      <c r="C47" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D47" s="18">
+      <c r="D47" s="17">
         <v>1</v>
       </c>
-      <c r="E47" s="22">
+      <c r="E47" s="21">
         <v>45596</v>
       </c>
-      <c r="F47" s="37"/>
-      <c r="G47" s="21">
+      <c r="F47" s="36"/>
+      <c r="G47" s="20">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H47" s="18"/>
-      <c r="I47" s="18"/>
-      <c r="J47" s="18"/>
-      <c r="K47" s="18"/>
-      <c r="L47" s="22"/>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="51">
-        <f t="shared" ref="A48:A110" si="3">IF(B48="","",IF(D48=D47,A47+1,(D48*100)))</f>
+      <c r="H47" s="17"/>
+      <c r="I47" s="17"/>
+      <c r="J47" s="17"/>
+      <c r="K47" s="17"/>
+      <c r="L47" s="21"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A48" s="50">
+        <f t="shared" ref="A48:A111" si="3">IF(B48="","",IF(D48=D47,A47+1,(D48*100)))</f>
         <v>101</v>
       </c>
       <c r="B48" s="5" t="s">
@@ -2374,10 +2530,13 @@
         <v>1</v>
       </c>
       <c r="E48" s="12">
-        <v>45638</v>
+        <v>45600</v>
+      </c>
+      <c r="F48" s="12">
+        <v>45600</v>
       </c>
       <c r="G48" s="6">
-        <f t="shared" ref="G48:G110" si="4">IF(B48="","",IF(AND(E48&gt;0,F48&gt;0),F48-E48,0))</f>
+        <f t="shared" ref="G48:G111" si="4">IF(B48="","",IF(AND(E48&gt;0,F48&gt;0),F48-E48,0))</f>
         <v>0</v>
       </c>
       <c r="H48" s="6" t="s">
@@ -2385,8 +2544,8 @@
       </c>
       <c r="L48" s="12"/>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A49" s="60">
+    <row r="49" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="59">
         <f t="shared" si="3"/>
         <v>102</v>
       </c>
@@ -2399,7 +2558,7 @@
       <c r="D49" s="6">
         <v>1</v>
       </c>
-      <c r="E49" s="12">
+      <c r="E49" s="76">
         <v>45638</v>
       </c>
       <c r="F49" s="12">
@@ -2414,8 +2573,8 @@
       </c>
       <c r="L49" s="12"/>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A50" s="60">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A50" s="59">
         <f t="shared" si="3"/>
         <v>103</v>
       </c>
@@ -2439,13 +2598,16 @@
         <f t="shared" si="4"/>
         <v>-34</v>
       </c>
+      <c r="H50" s="6" t="s">
+        <v>97</v>
+      </c>
       <c r="L50" s="12"/>
-      <c r="M50" s="25" t="s">
+      <c r="M50" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A51" s="60">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A51" s="59">
         <f t="shared" si="3"/>
         <v>104</v>
       </c>
@@ -2468,10 +2630,13 @@
         <f t="shared" si="4"/>
         <v>-4</v>
       </c>
+      <c r="H51" s="6" t="s">
+        <v>97</v>
+      </c>
       <c r="L51" s="12"/>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A52" s="60">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A52" s="59">
         <f t="shared" si="3"/>
         <v>105</v>
       </c>
@@ -2494,484 +2659,556 @@
         <f t="shared" si="4"/>
         <v>-1</v>
       </c>
+      <c r="H52" s="6" t="s">
+        <v>104</v>
+      </c>
       <c r="L52" s="12"/>
     </row>
-    <row r="53" spans="1:13" s="15" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="60">
-        <f t="shared" si="3"/>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A53" s="50">
+        <f>IF(B53="","",IF(D53=D52,A52+1,(D53*100)))</f>
         <v>106</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C53" s="10" t="s">
+      <c r="C53" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D53" s="10">
+      <c r="D53" s="6">
         <v>1</v>
       </c>
-      <c r="E53" s="14">
-        <v>45596</v>
-      </c>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10">
+      <c r="E53" s="12">
+        <v>45600</v>
+      </c>
+      <c r="F53" s="12">
+        <v>45600</v>
+      </c>
+      <c r="G53" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10"/>
-      <c r="K53" s="10"/>
-      <c r="L53" s="14"/>
-      <c r="M53" s="26"/>
-    </row>
-    <row r="54" spans="1:13" s="16" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="51">
-        <f t="shared" si="3"/>
+      <c r="H53" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="L53" s="12"/>
+    </row>
+    <row r="54" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D54" s="6">
+        <v>1</v>
+      </c>
+      <c r="E54" s="77">
+        <v>45600</v>
+      </c>
+      <c r="F54" s="12">
+        <v>45600</v>
+      </c>
+      <c r="G54" s="6">
+        <f>IF(B54="","",IF(AND(E54&gt;0,F54&gt;0),F54-E54,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="L54" s="12"/>
+    </row>
+    <row r="55" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D55" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E55" s="77">
+        <v>45602</v>
+      </c>
+      <c r="F55" s="12"/>
+      <c r="L55" s="12"/>
+    </row>
+    <row r="56" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D56" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E56" s="77">
+        <v>45602</v>
+      </c>
+      <c r="F56" s="12"/>
+      <c r="L56" s="12"/>
+    </row>
+    <row r="57" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="50">
+        <f>IF(B57="","",IF(D57=Sheet1!D54,Sheet1!A54+1,(D57*100)))</f>
+        <v>110.00000000000001</v>
+      </c>
+      <c r="B57" s="5" t="str">
+        <f>"Iteration "&amp;D57&amp;" Test Report"</f>
+        <v>Iteration 1.1 Test Report</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D57" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E57" s="49">
+        <v>45603</v>
+      </c>
+      <c r="G57" s="6">
+        <f>IF(B57="","",IF(AND(E57&gt;0,F57&gt;0),F57-E57,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L57" s="12"/>
+      <c r="M57" s="24" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" s="75" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="68">
+        <f>IF(B58="","",IF(D58=D53,A53+1,(D58*100)))</f>
         <v>200</v>
       </c>
-      <c r="B54" s="2" t="str">
-        <f>"Iteration " &amp; D54 &amp; " Completion"</f>
+      <c r="B58" s="69" t="str">
+        <f>"Iteration " &amp; D58 &amp; " Completion"</f>
         <v>Iteration 2 Completion</v>
       </c>
-      <c r="C54" s="18" t="s">
+      <c r="C58" s="70" t="s">
         <v>37</v>
       </c>
-      <c r="D54" s="1">
+      <c r="D58" s="70">
         <v>2</v>
       </c>
-      <c r="E54" s="50">
-        <v>45601</v>
-      </c>
-      <c r="F54" s="1"/>
-      <c r="G54" s="6">
+      <c r="E58" s="71">
+        <v>45608</v>
+      </c>
+      <c r="F58" s="70"/>
+      <c r="G58" s="72">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="12"/>
-      <c r="M54" s="34"/>
-    </row>
-    <row r="55" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="51">
+      <c r="H58" s="70"/>
+      <c r="I58" s="70"/>
+      <c r="J58" s="70"/>
+      <c r="K58" s="70"/>
+      <c r="L58" s="73"/>
+      <c r="M58" s="74"/>
+    </row>
+    <row r="59" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A59" s="50">
+        <f>IF(B59="","",IF(D59=D54,A54+1,(D59*100)))</f>
+        <v>200</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D59" s="6">
+        <v>2</v>
+      </c>
+      <c r="E59" s="49">
+        <v>45606</v>
+      </c>
+      <c r="G59" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="L59" s="12"/>
+    </row>
+    <row r="60" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A60" s="50">
         <f t="shared" si="3"/>
         <v>201</v>
       </c>
-      <c r="B55" s="5" t="str">
-        <f>"Iteration "&amp;D55-1&amp;" Test Report"</f>
-        <v>Iteration 1 Test Report</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D55" s="6">
+      <c r="B60" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D60" s="6">
         <v>2</v>
       </c>
-      <c r="E55" s="50">
-        <f t="shared" ref="E55:E118" si="5">IF(B55="","",IF(D55=D54,E54,E54+14))</f>
-        <v>45601</v>
-      </c>
-      <c r="G55" s="6">
+      <c r="E60" s="49">
+        <f t="shared" ref="E60:E119" si="5">IF(B60="","",IF(D60=D59,E59,E59+14))</f>
+        <v>45606</v>
+      </c>
+      <c r="G60" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L55" s="12"/>
-      <c r="M55" s="25" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="51">
+      <c r="H60" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="L60" s="12"/>
+    </row>
+    <row r="61" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A61" s="50">
         <f t="shared" si="3"/>
         <v>202</v>
       </c>
-      <c r="B56" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D56" s="6">
+      <c r="B61" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D61" s="6">
+        <f>IF(B61="","",D60)</f>
         <v>2</v>
       </c>
-      <c r="E56" s="50">
+      <c r="E61" s="49">
         <f t="shared" si="5"/>
-        <v>45601</v>
-      </c>
-      <c r="G56" s="6">
+        <v>45606</v>
+      </c>
+      <c r="G61" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L56" s="12"/>
-    </row>
-    <row r="57" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="51">
+      <c r="H61" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="L61" s="12"/>
+    </row>
+    <row r="62" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A62" s="50">
         <f t="shared" si="3"/>
         <v>203</v>
       </c>
-      <c r="B57" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D57" s="6">
+      <c r="B62" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D62" s="6">
+        <f t="shared" ref="D62:D123" si="6">IF(B62="","",D61)</f>
         <v>2</v>
       </c>
-      <c r="E57" s="50">
+      <c r="E62" s="49">
         <f t="shared" si="5"/>
-        <v>45601</v>
-      </c>
-      <c r="G57" s="6">
+        <v>45606</v>
+      </c>
+      <c r="G62" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L57" s="12"/>
-    </row>
-    <row r="58" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="51">
+      <c r="H62" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="L62" s="12"/>
+    </row>
+    <row r="63" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A63" s="50">
         <f t="shared" si="3"/>
         <v>204</v>
       </c>
-      <c r="B58" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D58" s="6">
-        <f>IF(B58="","",D57)</f>
-        <v>2</v>
-      </c>
-      <c r="E58" s="50">
-        <f t="shared" si="5"/>
-        <v>45601</v>
-      </c>
-      <c r="G58" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L58" s="12"/>
-    </row>
-    <row r="59" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="51">
-        <f t="shared" si="3"/>
-        <v>205</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D59" s="6">
-        <f t="shared" ref="D59:D122" si="6">IF(B59="","",D58)</f>
-        <v>2</v>
-      </c>
-      <c r="E59" s="50">
-        <f t="shared" si="5"/>
-        <v>45601</v>
-      </c>
-      <c r="G59" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L59" s="12"/>
-    </row>
-    <row r="60" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="51">
-        <f t="shared" si="3"/>
-        <v>206</v>
-      </c>
-      <c r="B60" s="5" t="s">
+      <c r="B63" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C63" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D60" s="6">
+      <c r="D63" s="6">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="E60" s="50">
+      <c r="E63" s="49">
         <f t="shared" si="5"/>
-        <v>45601</v>
-      </c>
-      <c r="G60" s="6">
+        <v>45606</v>
+      </c>
+      <c r="G63" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L60" s="12"/>
-    </row>
-    <row r="61" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="51" t="str">
+      <c r="H63" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="L63" s="12">
+        <f t="shared" ref="L63:L111" si="7">IF(B63="","",IF(D63=D62,L62,IF(F63&gt;0,F63,"Not Delivered")))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A64" s="50">
+        <f>IF(B64="","",IF(D64=D69,A69+1,(D64*100)))</f>
+        <v>207</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D64" s="6">
+        <f>IF(B64="","",D69)</f>
+        <v>2</v>
+      </c>
+      <c r="E64" s="49">
+        <f>IF(B64="","",IF(D64=D69,E69,E69+14))</f>
+        <v>45606</v>
+      </c>
+      <c r="G64" s="6">
+        <f>IF(B64="","",IF(AND(E64&gt;0,F64&gt;0),F64-E64,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L64" s="12">
+        <f>IF(B64="","",IF(D64=D69,L69,IF(F64&gt;0,F64,"Not Delivered")))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A65" s="50">
+        <f>IF(B65="","",IF(D65=D64,A64+1,(D65*100)))</f>
+        <v>208</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D65" s="6">
+        <f t="shared" ref="D65:D67" si="8">IF(B65="","",D64)</f>
+        <v>2</v>
+      </c>
+      <c r="E65" s="49">
+        <f>IF(B65="","",IF(D65=D64,E64,E64+14))</f>
+        <v>45606</v>
+      </c>
+      <c r="G65" s="6">
+        <f>IF(B65="","",IF(AND(E65&gt;0,F65&gt;0),F65-E65,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L65" s="12">
+        <f t="shared" ref="L65:L67" si="9">IF(B65="","",IF(D65=D64,L64,IF(F65&gt;0,F65,"Not Delivered")))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A66" s="50">
+        <f>IF(B66="","",IF(D66=D65,A65+1,(D66*100)))</f>
+        <v>209</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D66" s="6">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="E66" s="49">
+        <f>IF(B66="","",IF(D66=D65,E65,E65+14))</f>
+        <v>45606</v>
+      </c>
+      <c r="G66" s="6">
+        <f>IF(B66="","",IF(AND(E66&gt;0,F66&gt;0),F66-E66,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L66" s="12">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A67" s="50">
+        <f>IF(B67="","",IF(D67=D66,A66+1,(D67*100)))</f>
+        <v>210</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D67" s="6">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="E67" s="49">
+        <f>IF(B67="","",IF(D67=D66,E66,E66+14))</f>
+        <v>45606</v>
+      </c>
+      <c r="G67" s="6">
+        <f>IF(B67="","",IF(AND(E67&gt;0,F67&gt;0),F67-E67,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L67" s="12">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A68" s="50">
+        <f>IF(B68="","",IF(D68=D63,A63+1,(D68*100)))</f>
+        <v>205</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D68" s="6">
+        <f>IF(B68="","",D63)</f>
+        <v>2</v>
+      </c>
+      <c r="E68" s="49">
+        <f>IF(B68="","",IF(D68=D63,E63,E63+14))</f>
+        <v>45606</v>
+      </c>
+      <c r="G68" s="6">
+        <f>IF(B68="","",IF(AND(E68&gt;0,F68&gt;0),F68-E68,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L68" s="12">
+        <f>IF(B68="","",IF(D68=D63,L63,IF(F68&gt;0,F68,"Not Delivered")))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A69" s="50">
+        <f>IF(B69="","",IF(D69=D68,A68+1,(D69*100)))</f>
+        <v>206</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D69" s="6">
+        <f>IF(B69="","",D68)</f>
+        <v>2</v>
+      </c>
+      <c r="E69" s="49">
+        <f>IF(B69="","",IF(D69=D68,E68,E68+14))</f>
+        <v>45606</v>
+      </c>
+      <c r="G69" s="6">
+        <f>IF(B69="","",IF(AND(E69&gt;0,F69&gt;0),F69-E69,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L69" s="12">
+        <f>IF(B69="","",IF(D69=D68,L68,IF(F69&gt;0,F69,"Not Delivered")))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A70" s="50">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D61" s="6" t="str">
+        <v>207</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D70" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E61" s="50" t="str">
+        <v>2</v>
+      </c>
+      <c r="E70" s="49">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G61" s="6" t="str">
+        <v>45606</v>
+      </c>
+      <c r="G70" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L61" s="12" t="str">
-        <f t="shared" ref="L60:L110" si="7">IF(B61="","",IF(D61=D60,L60,IF(F61&gt;0,F61,"Not Delivered")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="51" t="str">
+        <v>0</v>
+      </c>
+      <c r="L70" s="12">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="50">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D62" s="6" t="str">
+        <v>208</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D71" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E62" s="50" t="str">
+        <v>2</v>
+      </c>
+      <c r="E71" s="49">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G62" s="6" t="str">
+        <v>45606</v>
+      </c>
+      <c r="G71" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L62" s="12" t="str">
+        <v>0</v>
+      </c>
+      <c r="L71" s="12">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="63" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D63" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E63" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G63" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L63" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A64" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D64" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E64" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G64" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L64" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="65" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D65" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E65" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G65" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L65" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D66" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E66" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G66" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L66" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D67" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E67" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G67" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L67" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A68" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D68" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E68" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G68" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L68" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="69" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A69" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D69" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E69" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G69" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L69" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A70" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D70" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E70" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G70" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L70" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A71" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D71" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E71" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G71" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L71" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A72" s="51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D72" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E72" s="50" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G72" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L72" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="51" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="50">
+        <f>IF(B72="","",IF(D72=Sheet1!D71,Sheet1!A71+1,(D72*100)))</f>
+        <v>209</v>
+      </c>
+      <c r="B72" s="5" t="str">
+        <f>"Iteration "&amp;D72&amp;" Test Report"</f>
+        <v>Iteration 2 Test Report</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D72" s="6">
+        <v>2</v>
+      </c>
+      <c r="E72" s="49">
+        <v>45607</v>
+      </c>
+      <c r="G72" s="6">
+        <f>IF(B72="","",IF(AND(E72&gt;0,F72&gt;0),F72-E72,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L72" s="12"/>
+      <c r="M72" s="24" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A73" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2979,7 +3216,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E73" s="50" t="str">
+      <c r="E73" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -2992,8 +3229,8 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="51" t="str">
+    <row r="74" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A74" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3001,7 +3238,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E74" s="50" t="str">
+      <c r="E74" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3014,8 +3251,8 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A75" s="51" t="str">
+    <row r="75" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A75" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3023,7 +3260,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E75" s="50" t="str">
+      <c r="E75" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3036,8 +3273,8 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="51" t="str">
+    <row r="76" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A76" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3045,7 +3282,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E76" s="50" t="str">
+      <c r="E76" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3058,8 +3295,8 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A77" s="51" t="str">
+    <row r="77" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A77" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3067,7 +3304,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E77" s="50" t="str">
+      <c r="E77" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3080,8 +3317,8 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A78" s="51" t="str">
+    <row r="78" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A78" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3089,7 +3326,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E78" s="50" t="str">
+      <c r="E78" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3102,8 +3339,8 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="51" t="str">
+    <row r="79" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A79" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3111,7 +3348,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E79" s="50" t="str">
+      <c r="E79" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3124,8 +3361,8 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="51" t="str">
+    <row r="80" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A80" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3133,7 +3370,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E80" s="50" t="str">
+      <c r="E80" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3146,8 +3383,8 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A81" s="51" t="str">
+    <row r="81" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A81" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3155,7 +3392,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E81" s="50" t="str">
+      <c r="E81" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3168,8 +3405,8 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A82" s="51" t="str">
+    <row r="82" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A82" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3177,7 +3414,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E82" s="50" t="str">
+      <c r="E82" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3190,8 +3427,8 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A83" s="51" t="str">
+    <row r="83" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A83" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3199,7 +3436,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E83" s="50" t="str">
+      <c r="E83" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3212,8 +3449,8 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A84" s="51" t="str">
+    <row r="84" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A84" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3221,7 +3458,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E84" s="50" t="str">
+      <c r="E84" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3234,8 +3471,8 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A85" s="51" t="str">
+    <row r="85" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A85" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3243,7 +3480,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E85" s="50" t="str">
+      <c r="E85" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3256,8 +3493,8 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A86" s="51" t="str">
+    <row r="86" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A86" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3265,7 +3502,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E86" s="50" t="str">
+      <c r="E86" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3278,8 +3515,8 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A87" s="51" t="str">
+    <row r="87" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A87" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3287,7 +3524,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E87" s="50" t="str">
+      <c r="E87" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3300,8 +3537,8 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A88" s="51" t="str">
+    <row r="88" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A88" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3309,7 +3546,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E88" s="50" t="str">
+      <c r="E88" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3322,8 +3559,8 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A89" s="51" t="str">
+    <row r="89" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A89" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3331,7 +3568,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E89" s="50" t="str">
+      <c r="E89" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3344,8 +3581,8 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A90" s="51" t="str">
+    <row r="90" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A90" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3353,7 +3590,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E90" s="50" t="str">
+      <c r="E90" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3366,8 +3603,8 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A91" s="51" t="str">
+    <row r="91" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A91" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3375,7 +3612,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E91" s="50" t="str">
+      <c r="E91" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3388,8 +3625,8 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" s="51" t="str">
+    <row r="92" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A92" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3397,7 +3634,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E92" s="50" t="str">
+      <c r="E92" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3410,8 +3647,8 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="51" t="str">
+    <row r="93" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A93" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3419,7 +3656,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E93" s="50" t="str">
+      <c r="E93" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3432,8 +3669,8 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A94" s="51" t="str">
+    <row r="94" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A94" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3441,7 +3678,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E94" s="50" t="str">
+      <c r="E94" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3454,8 +3691,8 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A95" s="51" t="str">
+    <row r="95" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A95" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3463,7 +3700,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E95" s="50" t="str">
+      <c r="E95" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3476,8 +3713,8 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A96" s="51" t="str">
+    <row r="96" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A96" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3485,7 +3722,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E96" s="50" t="str">
+      <c r="E96" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3498,8 +3735,8 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A97" s="51" t="str">
+    <row r="97" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A97" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3507,7 +3744,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E97" s="50" t="str">
+      <c r="E97" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3520,8 +3757,8 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A98" s="51" t="str">
+    <row r="98" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A98" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3529,7 +3766,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E98" s="50" t="str">
+      <c r="E98" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3542,8 +3779,8 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A99" s="51" t="str">
+    <row r="99" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A99" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3551,7 +3788,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E99" s="50" t="str">
+      <c r="E99" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3564,8 +3801,8 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A100" s="51" t="str">
+    <row r="100" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A100" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3573,7 +3810,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E100" s="50" t="str">
+      <c r="E100" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3586,8 +3823,8 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A101" s="51" t="str">
+    <row r="101" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A101" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3595,7 +3832,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E101" s="50" t="str">
+      <c r="E101" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3608,8 +3845,8 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A102" s="51" t="str">
+    <row r="102" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A102" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3617,7 +3854,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E102" s="50" t="str">
+      <c r="E102" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3630,8 +3867,8 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A103" s="51" t="str">
+    <row r="103" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A103" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3639,7 +3876,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E103" s="50" t="str">
+      <c r="E103" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3652,8 +3889,8 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A104" s="51" t="str">
+    <row r="104" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A104" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3661,7 +3898,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E104" s="50" t="str">
+      <c r="E104" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3674,8 +3911,8 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="51" t="str">
+    <row r="105" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A105" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3683,7 +3920,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E105" s="50" t="str">
+      <c r="E105" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3696,8 +3933,8 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A106" s="51" t="str">
+    <row r="106" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A106" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3705,7 +3942,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E106" s="50" t="str">
+      <c r="E106" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3718,8 +3955,8 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A107" s="51" t="str">
+    <row r="107" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A107" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3727,7 +3964,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E107" s="50" t="str">
+      <c r="E107" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3740,8 +3977,8 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A108" s="51" t="str">
+    <row r="108" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A108" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3749,7 +3986,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E108" s="50" t="str">
+      <c r="E108" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3762,8 +3999,8 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A109" s="51" t="str">
+    <row r="109" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A109" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3771,7 +4008,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E109" s="50" t="str">
+      <c r="E109" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3784,8 +4021,8 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A110" s="51" t="str">
+    <row r="110" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A110" s="50" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3793,7 +4030,7 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E110" s="50" t="str">
+      <c r="E110" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3806,1284 +4043,1308 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A111" s="51" t="str">
-        <f t="shared" ref="A111:A168" si="8">IF(B111="","",IF(D111=D110,A110+1,(D111*100)))</f>
+    <row r="111" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A111" s="50" t="str">
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D111" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E111" s="50" t="str">
+      <c r="E111" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G111" s="6" t="str">
-        <f t="shared" ref="G111:G168" si="9">IF(B111="","",IF(AND(E111&gt;0,F111&gt;0),F111-E111,0))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L111" s="12" t="str">
-        <f t="shared" ref="L111:L168" si="10">IF(B111="","",IF(D111=D110,L110,IF(F111&gt;0,F111,"Not Delivered")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A112" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="112" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A112" s="50" t="str">
+        <f t="shared" ref="A112:A169" si="10">IF(B112="","",IF(D112=D111,A111+1,(D112*100)))</f>
         <v/>
       </c>
       <c r="D112" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E112" s="50" t="str">
+      <c r="E112" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G112" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="G112:G169" si="11">IF(B112="","",IF(AND(E112&gt;0,F112&gt;0),F112-E112,0))</f>
         <v/>
       </c>
       <c r="L112" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="113" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A113" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="L112:L169" si="12">IF(B112="","",IF(D112=D111,L111,IF(F112&gt;0,F112,"Not Delivered")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A113" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D113" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E113" s="50" t="str">
+      <c r="E113" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G113" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L113" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="114" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A114" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="114" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A114" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D114" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E114" s="50" t="str">
+      <c r="E114" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G114" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L114" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="115" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A115" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A115" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D115" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E115" s="50" t="str">
+      <c r="E115" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G115" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L115" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="116" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A116" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="116" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A116" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D116" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E116" s="50" t="str">
+      <c r="E116" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G116" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L116" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="117" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="117" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A117" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D117" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E117" s="50" t="str">
+      <c r="E117" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G117" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L117" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="118" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A118" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A118" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D118" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E118" s="50" t="str">
+      <c r="E118" s="49" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G118" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L118" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="119" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A119" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="119" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A119" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D119" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E119" s="50" t="str">
-        <f t="shared" ref="E119:E168" si="11">IF(B119="","",IF(D119=D118,E118,E118+14))</f>
+      <c r="E119" s="49" t="str">
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G119" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L119" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="120" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A120" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="120" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A120" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D120" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E120" s="50" t="str">
-        <f t="shared" si="11"/>
+      <c r="E120" s="49" t="str">
+        <f t="shared" ref="E120:E169" si="13">IF(B120="","",IF(D120=D119,E119,E119+14))</f>
         <v/>
       </c>
       <c r="G120" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L120" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="121" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A121" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="121" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A121" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D121" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E121" s="50" t="str">
-        <f t="shared" si="11"/>
+      <c r="E121" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G121" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L121" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="122" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A122" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="122" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A122" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D122" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E122" s="50" t="str">
-        <f t="shared" si="11"/>
+      <c r="E122" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G122" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L122" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="123" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A123" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="123" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A123" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D123" s="6" t="str">
-        <f t="shared" ref="D123:D168" si="12">IF(B123="","",D122)</f>
-        <v/>
-      </c>
-      <c r="E123" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E123" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G123" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L123" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="124" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A124" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="124" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A124" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D124" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E124" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="D124:D169" si="14">IF(B124="","",D123)</f>
+        <v/>
+      </c>
+      <c r="E124" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G124" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L124" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="125" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A125" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="125" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A125" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D125" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E125" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E125" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G125" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L125" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="126" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A126" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A126" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D126" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E126" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E126" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G126" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L126" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="127" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A127" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="127" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A127" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D127" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E127" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E127" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G127" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L127" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="128" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A128" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="128" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A128" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D128" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E128" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E128" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G128" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L128" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="129" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A129" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="129" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A129" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D129" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E129" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E129" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G129" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L129" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="130" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A130" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="130" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A130" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D130" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E130" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E130" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G130" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L130" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="131" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A131" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="131" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A131" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D131" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E131" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E131" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G131" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L131" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="132" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A132" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="132" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A132" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D132" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E132" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E132" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G132" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L132" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="133" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A133" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="133" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A133" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D133" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E133" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E133" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G133" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L133" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="134" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A134" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="134" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A134" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D134" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E134" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E134" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G134" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L134" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="135" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A135" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="135" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A135" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D135" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E135" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E135" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G135" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L135" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="136" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A136" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A136" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D136" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E136" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E136" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G136" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L136" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="137" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A137" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="137" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A137" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D137" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E137" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E137" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G137" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L137" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="138" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A138" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="138" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A138" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D138" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E138" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E138" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G138" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L138" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="139" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A139" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="139" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A139" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D139" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E139" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E139" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G139" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L139" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="140" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A140" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A140" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D140" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E140" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E140" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G140" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L140" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="141" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A141" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A141" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D141" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E141" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E141" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G141" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L141" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="142" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A142" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="142" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A142" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D142" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E142" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E142" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G142" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L142" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="143" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A143" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="143" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A143" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D143" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E143" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E143" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G143" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L143" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="144" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A144" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="144" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A144" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D144" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E144" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E144" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G144" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L144" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="145" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A145" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="145" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A145" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D145" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E145" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E145" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G145" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L145" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="146" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A146" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A146" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D146" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E146" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E146" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G146" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L146" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="147" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A147" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="147" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A147" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D147" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E147" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E147" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G147" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L147" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="148" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A148" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="148" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A148" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D148" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E148" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E148" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G148" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L148" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="149" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A149" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="149" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A149" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D149" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E149" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E149" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G149" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L149" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="150" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A150" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="150" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A150" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D150" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E150" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E150" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G150" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L150" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="151" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A151" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A151" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D151" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E151" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E151" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G151" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L151" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="152" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A152" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="152" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A152" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D152" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E152" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E152" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G152" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L152" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="153" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A153" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="153" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A153" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D153" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E153" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E153" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G153" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L153" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="154" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A154" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="154" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A154" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D154" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E154" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E154" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G154" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L154" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="155" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A155" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="155" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A155" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D155" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E155" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E155" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G155" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L155" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="156" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A156" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="156" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A156" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D156" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E156" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E156" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G156" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L156" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="157" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A157" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A157" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D157" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E157" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E157" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G157" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L157" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="158" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A158" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A158" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D158" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E158" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E158" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G158" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L158" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="159" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A159" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A159" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D159" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E159" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E159" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G159" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L159" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="160" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A160" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="160" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A160" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D160" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E160" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E160" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G160" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L160" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="161" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A161" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="161" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A161" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D161" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E161" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E161" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G161" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L161" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="162" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A162" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="162" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A162" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D162" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E162" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E162" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G162" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L162" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="163" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A163" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="163" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A163" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D163" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E163" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E163" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G163" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L163" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="164" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A164" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="164" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A164" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D164" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E164" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E164" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G164" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L164" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="165" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A165" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="165" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A165" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D165" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E165" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E165" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G165" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L165" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="166" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A166" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A166" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D166" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E166" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E166" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G166" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L166" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="167" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A167" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="167" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A167" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D167" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E167" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E167" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G167" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L167" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="168" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A168" s="51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="168" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A168" s="50" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D168" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E168" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E168" s="49" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G168" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="L168" s="12" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="169" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A169" s="50" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="D169" s="6" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="E169" s="49" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="G169" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="L169" s="12" t="str">
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="M35:M39"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A12:A13"/>
@@ -5099,11 +5360,57 @@
     <mergeCell ref="M9:M11"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H9:K9"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="M35:M39"/>
   </mergeCells>
-  <conditionalFormatting sqref="G14:G168">
+  <conditionalFormatting sqref="G73:G169 G14:G56 G58:G63 G70:G71">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G57">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G72">
     <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G64:G69">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G10:G1048576">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/project requirements spreadsheet.xlsx
+++ b/project requirements spreadsheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Documents\__ School\CS 3300- Software Development\Project (Group 1)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Documents\__ School\CS 3300- Software Development\Project (Group 1)\Shattered-Protocols-Text-RPG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7444EF99-CFC3-4F27-AEF9-1A3E76CB8983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E74DDA9-B193-4FFF-8259-E030B8CE806C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" xr2:uid="{CAB5D44A-E176-404C-B398-BEAD2D9E6884}"/>
+    <workbookView xWindow="-28908" yWindow="-108" windowWidth="29016" windowHeight="15972" xr2:uid="{CAB5D44A-E176-404C-B398-BEAD2D9E6884}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="120">
   <si>
     <t>Intro to Software Engineering</t>
   </si>
@@ -382,9 +382,6 @@
     <t>key item ends game properly</t>
   </si>
   <si>
-    <t>Generate Gameplay Test Document</t>
-  </si>
-  <si>
     <t>S Welton / J Hong</t>
   </si>
   <si>
@@ -394,13 +391,19 @@
     <t>*(If time) Break Puzzles into Clue Items so passwords arent provided with puzzle</t>
   </si>
   <si>
-    <t>*(If Time) Doors locking.unliocking</t>
-  </si>
-  <si>
     <t>Start Dev Document</t>
   </si>
   <si>
     <t>Intro/Outro Text Display</t>
+  </si>
+  <si>
+    <t>I ended up having to do a LOT of code this iteration, so pushed this off to next iteration</t>
+  </si>
+  <si>
+    <t>Doors locking.unliocking</t>
+  </si>
+  <si>
+    <t>Generate Gameplay Test File</t>
   </si>
 </sst>
 </file>
@@ -897,6 +900,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -925,9 +931,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1293,51 +1296,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="31" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="82" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="82"/>
+      <c r="B1" s="83"/>
       <c r="C1" s="28"/>
-      <c r="D1" s="87" t="s">
+      <c r="D1" s="88" t="s">
         <v>91</v>
       </c>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
-      <c r="J1" s="87"/>
-      <c r="K1" s="87"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
       <c r="L1" s="28"/>
       <c r="M1" s="30"/>
     </row>
     <row r="2" spans="1:13" s="31" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A2" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="84"/>
+      <c r="A2" s="84" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="85"/>
       <c r="C2" s="28"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="87"/>
-      <c r="J2" s="87"/>
-      <c r="K2" s="87"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="51"/>
       <c r="B3" s="38"/>
       <c r="C3" s="13"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="87"/>
-      <c r="I3" s="87"/>
-      <c r="J3" s="87"/>
-      <c r="K3" s="87"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
       <c r="L3" s="13"/>
       <c r="M3" s="13"/>
     </row>
@@ -1348,14 +1351,14 @@
       <c r="B4" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="87"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="87"/>
-      <c r="I4" s="87"/>
-      <c r="J4" s="87"/>
-      <c r="K4" s="87"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
+      <c r="K4" s="88"/>
     </row>
     <row r="5" spans="1:13" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="52" t="s">
@@ -1364,14 +1367,14 @@
       <c r="B5" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="87"/>
-      <c r="E5" s="87"/>
-      <c r="F5" s="87"/>
-      <c r="G5" s="87"/>
-      <c r="H5" s="87"/>
-      <c r="I5" s="87"/>
-      <c r="J5" s="87"/>
-      <c r="K5" s="87"/>
+      <c r="D5" s="88"/>
+      <c r="E5" s="88"/>
+      <c r="F5" s="88"/>
+      <c r="G5" s="88"/>
+      <c r="H5" s="88"/>
+      <c r="I5" s="88"/>
+      <c r="J5" s="88"/>
+      <c r="K5" s="88"/>
     </row>
     <row r="6" spans="1:13" s="7" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="53" t="s">
@@ -1380,14 +1383,14 @@
       <c r="B6" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="D6" s="87"/>
-      <c r="E6" s="87"/>
-      <c r="F6" s="87"/>
-      <c r="G6" s="87"/>
-      <c r="H6" s="87"/>
-      <c r="I6" s="87"/>
-      <c r="J6" s="87"/>
-      <c r="K6" s="87"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="88"/>
+      <c r="F6" s="88"/>
+      <c r="G6" s="88"/>
+      <c r="H6" s="88"/>
+      <c r="I6" s="88"/>
+      <c r="J6" s="88"/>
+      <c r="K6" s="88"/>
       <c r="L6" s="1"/>
       <c r="M6" s="32"/>
     </row>
@@ -1407,38 +1410,38 @@
       <c r="M7" s="32"/>
     </row>
     <row r="8" spans="1:13" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="88" t="s">
+      <c r="A8" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="88"/>
-      <c r="C8" s="88"/>
-      <c r="D8" s="88"/>
-      <c r="E8" s="88"/>
-      <c r="F8" s="88"/>
-      <c r="G8" s="88"/>
-      <c r="H8" s="88"/>
-      <c r="I8" s="88"/>
-      <c r="J8" s="88"/>
-      <c r="K8" s="88"/>
-      <c r="L8" s="88"/>
-      <c r="M8" s="88"/>
+      <c r="B8" s="78"/>
+      <c r="C8" s="78"/>
+      <c r="D8" s="78"/>
+      <c r="E8" s="78"/>
+      <c r="F8" s="78"/>
+      <c r="G8" s="78"/>
+      <c r="H8" s="78"/>
+      <c r="I8" s="78"/>
+      <c r="J8" s="78"/>
+      <c r="K8" s="78"/>
+      <c r="L8" s="78"/>
+      <c r="M8" s="78"/>
     </row>
     <row r="9" spans="1:13" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="88" t="s">
+      <c r="C9" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="88"/>
-      <c r="E9" s="88"/>
-      <c r="F9" s="88"/>
+      <c r="D9" s="78"/>
+      <c r="E9" s="78"/>
+      <c r="F9" s="78"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="88" t="s">
+      <c r="H9" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="88"/>
-      <c r="J9" s="88"/>
-      <c r="K9" s="88"/>
+      <c r="I9" s="78"/>
+      <c r="J9" s="78"/>
+      <c r="K9" s="78"/>
       <c r="L9" s="89" t="s">
         <v>20</v>
       </c>
@@ -1449,26 +1452,26 @@
     <row r="10" spans="1:13" s="7" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="78" t="s">
+      <c r="C10" s="79" t="s">
         <v>21</v>
       </c>
       <c r="D10" s="1"/>
-      <c r="E10" s="78" t="s">
+      <c r="E10" s="79" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="78" t="s">
+      <c r="F10" s="79" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="78" t="s">
+      <c r="G10" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="H10" s="78" t="s">
+      <c r="H10" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="I10" s="78" t="s">
+      <c r="I10" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="78" t="s">
+      <c r="J10" s="79" t="s">
         <v>5</v>
       </c>
       <c r="K10" s="1"/>
@@ -1482,16 +1485,16 @@
       <c r="B11" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="78"/>
+      <c r="C11" s="79"/>
       <c r="D11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="78"/>
-      <c r="J11" s="78"/>
+      <c r="E11" s="79"/>
+      <c r="F11" s="79"/>
+      <c r="G11" s="79"/>
+      <c r="H11" s="79"/>
+      <c r="I11" s="79"/>
+      <c r="J11" s="79"/>
       <c r="K11" s="29" t="s">
         <v>6</v>
       </c>
@@ -1499,7 +1502,7 @@
       <c r="M11" s="90"/>
     </row>
     <row r="12" spans="1:13" s="67" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="85" t="s">
+      <c r="A12" s="86" t="s">
         <v>40</v>
       </c>
       <c r="B12" s="62"/>
@@ -1526,7 +1529,7 @@
       <c r="M12" s="66"/>
     </row>
     <row r="13" spans="1:13" s="3" customFormat="1" ht="61.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="86"/>
+      <c r="A13" s="87"/>
       <c r="B13" s="8"/>
       <c r="C13" s="10"/>
       <c r="D13" s="10" t="s">
@@ -2141,7 +2144,7 @@
         <v>97</v>
       </c>
       <c r="L35" s="12"/>
-      <c r="M35" s="79" t="s">
+      <c r="M35" s="80" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2173,7 +2176,7 @@
         <v>97</v>
       </c>
       <c r="L36" s="12"/>
-      <c r="M36" s="80"/>
+      <c r="M36" s="81"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="59">
@@ -2203,7 +2206,7 @@
         <v>97</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="M37" s="80"/>
+      <c r="M37" s="81"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="59">
@@ -2233,7 +2236,7 @@
         <v>97</v>
       </c>
       <c r="L38" s="12"/>
-      <c r="M38" s="80"/>
+      <c r="M38" s="81"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="59">
@@ -2263,7 +2266,7 @@
         <v>97</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="80"/>
+      <c r="M39" s="81"/>
     </row>
     <row r="40" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" s="59">
@@ -2915,9 +2918,8 @@
         <f t="shared" ref="D62:D124" si="6">IF(B62="","",D61)</f>
         <v>2</v>
       </c>
-      <c r="E62" s="49">
-        <f t="shared" si="5"/>
-        <v>45606</v>
+      <c r="E62" s="49" t="s">
+        <v>83</v>
       </c>
       <c r="G62" s="6">
         <f t="shared" si="4"/>
@@ -2927,6 +2929,9 @@
         <v>97</v>
       </c>
       <c r="L62" s="12"/>
+      <c r="M62" s="24" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="63" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="50">
@@ -2944,7 +2949,6 @@
         <v>2</v>
       </c>
       <c r="E63" s="49">
-        <f t="shared" si="5"/>
         <v>45606</v>
       </c>
       <c r="G63" s="6">
@@ -3021,10 +3025,10 @@
         <v>209</v>
       </c>
       <c r="B66" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C66" s="6" t="s">
         <v>112</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>113</v>
       </c>
       <c r="D66" s="6">
         <f t="shared" si="9"/>
@@ -3049,7 +3053,7 @@
         <v>210</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>44</v>
@@ -3077,7 +3081,7 @@
         <v>205</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>44</v>
@@ -3105,7 +3109,7 @@
         <v>206</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>42</v>
@@ -3133,7 +3137,7 @@
         <v>207</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>44</v>
@@ -3189,7 +3193,7 @@
         <v>209</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>45</v>
@@ -5374,6 +5378,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="H10:H11"/>
     <mergeCell ref="H9:K9"/>
     <mergeCell ref="J10:J11"/>
     <mergeCell ref="M35:M39"/>
@@ -5390,7 +5395,6 @@
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="M9:M11"/>
-    <mergeCell ref="H10:H11"/>
   </mergeCells>
   <conditionalFormatting sqref="G10:G1048576">
     <cfRule type="colorScale" priority="1">

--- a/project requirements spreadsheet.xlsx
+++ b/project requirements spreadsheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Documents\__ School\CS 3300- Software Development\Project (Group 1)\Shattered-Protocols-Text-RPG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/soapmac/Documents/GitHub/Shattered-Protocols-Text-RPG/Shattered Protocols/Shattered-Protocols-Text-RPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E1FEBA5-135F-43FF-BF11-E2B7251CBB5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA6583C0-B331-9C44-9289-C2D774B87B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="29016" windowHeight="15816" xr2:uid="{CAB5D44A-E176-404C-B398-BEAD2D9E6884}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" xr2:uid="{CAB5D44A-E176-404C-B398-BEAD2D9E6884}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -892,12 +892,72 @@
     <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -921,66 +981,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1325,124 +1325,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B900A37F-814E-4AF4-9047-E946E2A67EEB}">
   <dimension ref="A1:M170"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.44140625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="15.5" style="6" customWidth="1"/>
     <col min="2" max="2" width="61.33203125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="17.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.1640625" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="12.6640625" style="6" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" style="6" customWidth="1"/>
+    <col min="8" max="8" width="16.1640625" style="6" customWidth="1"/>
     <col min="9" max="11" width="12.6640625" style="6" customWidth="1"/>
-    <col min="12" max="12" width="16.44140625" style="6" customWidth="1"/>
-    <col min="13" max="13" width="173.77734375" style="86" customWidth="1"/>
-    <col min="14" max="16384" width="9.109375" style="13"/>
+    <col min="12" max="12" width="16.5" style="6" customWidth="1"/>
+    <col min="13" max="13" width="173.83203125" style="75" customWidth="1"/>
+    <col min="14" max="16384" width="9.1640625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="27" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="69" t="s">
+    <row r="1" spans="1:13" s="27" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="89" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="70"/>
+      <c r="B1" s="90"/>
       <c r="C1" s="25"/>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="95" t="s">
         <v>91</v>
       </c>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="95"/>
       <c r="L1" s="25"/>
-      <c r="M1" s="78"/>
-    </row>
-    <row r="2" spans="1:13" s="27" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A2" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="72"/>
+      <c r="M1" s="67"/>
+    </row>
+    <row r="2" spans="1:13" s="27" customFormat="1" ht="19" x14ac:dyDescent="0.2">
+      <c r="A2" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="92"/>
       <c r="C2" s="25"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="75"/>
-      <c r="M2" s="79"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="M2" s="68"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="42"/>
       <c r="B3" s="30"/>
       <c r="C3" s="13"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
-      <c r="K3" s="75"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="95"/>
+      <c r="J3" s="95"/>
+      <c r="K3" s="95"/>
       <c r="L3" s="13"/>
-      <c r="M3" s="80"/>
-    </row>
-    <row r="4" spans="1:13" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="M3" s="69"/>
+    </row>
+    <row r="4" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="43" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
-      <c r="K4" s="75"/>
-      <c r="M4" s="81"/>
-    </row>
-    <row r="5" spans="1:13" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="95"/>
+      <c r="H4" s="95"/>
+      <c r="I4" s="95"/>
+      <c r="J4" s="95"/>
+      <c r="K4" s="95"/>
+      <c r="M4" s="70"/>
+    </row>
+    <row r="5" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="43" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="75"/>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="75"/>
-      <c r="K5" s="75"/>
-      <c r="M5" s="81"/>
-    </row>
-    <row r="6" spans="1:13" s="7" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D5" s="95"/>
+      <c r="E5" s="95"/>
+      <c r="F5" s="95"/>
+      <c r="G5" s="95"/>
+      <c r="H5" s="95"/>
+      <c r="I5" s="95"/>
+      <c r="J5" s="95"/>
+      <c r="K5" s="95"/>
+      <c r="M5" s="70"/>
+    </row>
+    <row r="6" spans="1:13" s="7" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="44" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="D6" s="75"/>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75"/>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
-      <c r="J6" s="75"/>
-      <c r="K6" s="75"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="95"/>
+      <c r="K6" s="95"/>
       <c r="L6" s="1"/>
-      <c r="M6" s="82"/>
-    </row>
-    <row r="7" spans="1:13" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="M6" s="71"/>
+    </row>
+    <row r="7" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="45"/>
       <c r="B7" s="2"/>
       <c r="C7" s="1"/>
@@ -1455,102 +1455,102 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
-      <c r="M7" s="82"/>
-    </row>
-    <row r="8" spans="1:13" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="68" t="s">
+      <c r="M7" s="71"/>
+    </row>
+    <row r="8" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="68"/>
-      <c r="C8" s="68"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="68"/>
-      <c r="K8" s="68"/>
-      <c r="L8" s="68"/>
-      <c r="M8" s="68"/>
-    </row>
-    <row r="9" spans="1:13" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B8" s="86"/>
+      <c r="C8" s="86"/>
+      <c r="D8" s="86"/>
+      <c r="E8" s="86"/>
+      <c r="F8" s="86"/>
+      <c r="G8" s="86"/>
+      <c r="H8" s="86"/>
+      <c r="I8" s="86"/>
+      <c r="J8" s="86"/>
+      <c r="K8" s="86"/>
+      <c r="L8" s="86"/>
+      <c r="M8" s="86"/>
+    </row>
+    <row r="9" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="68" t="s">
+      <c r="C9" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="68"/>
-      <c r="E9" s="68"/>
-      <c r="F9" s="68"/>
+      <c r="D9" s="86"/>
+      <c r="E9" s="86"/>
+      <c r="F9" s="86"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="68" t="s">
+      <c r="H9" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="68"/>
-      <c r="J9" s="68"/>
-      <c r="K9" s="68"/>
-      <c r="L9" s="76" t="s">
+      <c r="I9" s="86"/>
+      <c r="J9" s="86"/>
+      <c r="K9" s="86"/>
+      <c r="L9" s="96" t="s">
         <v>20</v>
       </c>
-      <c r="M9" s="77" t="s">
+      <c r="M9" s="83" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:13" s="7" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" s="7" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="67" t="s">
+      <c r="C10" s="85" t="s">
         <v>21</v>
       </c>
       <c r="D10" s="1"/>
-      <c r="E10" s="67" t="s">
+      <c r="E10" s="85" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="67" t="s">
+      <c r="F10" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="67" t="s">
+      <c r="G10" s="85" t="s">
         <v>60</v>
       </c>
-      <c r="H10" s="67" t="s">
+      <c r="H10" s="85" t="s">
         <v>4</v>
       </c>
-      <c r="I10" s="67" t="s">
+      <c r="I10" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="67" t="s">
+      <c r="J10" s="85" t="s">
         <v>5</v>
       </c>
       <c r="K10" s="1"/>
-      <c r="L10" s="76"/>
-      <c r="M10" s="77"/>
-    </row>
-    <row r="11" spans="1:13" s="7" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L10" s="96"/>
+      <c r="M10" s="83"/>
+    </row>
+    <row r="11" spans="1:13" s="7" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="67"/>
+      <c r="C11" s="85"/>
       <c r="D11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
-      <c r="J11" s="67"/>
+      <c r="E11" s="85"/>
+      <c r="F11" s="85"/>
+      <c r="G11" s="85"/>
+      <c r="H11" s="85"/>
+      <c r="I11" s="85"/>
+      <c r="J11" s="85"/>
       <c r="K11" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="L11" s="76"/>
-      <c r="M11" s="77"/>
-    </row>
-    <row r="12" spans="1:13" s="57" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="73" t="s">
+      <c r="L11" s="96"/>
+      <c r="M11" s="83"/>
+    </row>
+    <row r="12" spans="1:13" s="57" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="93" t="s">
         <v>40</v>
       </c>
       <c r="B12" s="53"/>
@@ -1574,10 +1574,10 @@
         <v>13</v>
       </c>
       <c r="L12" s="56"/>
-      <c r="M12" s="83"/>
-    </row>
-    <row r="13" spans="1:13" s="3" customFormat="1" ht="61.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="74"/>
+      <c r="M12" s="72"/>
+    </row>
+    <row r="13" spans="1:13" s="3" customFormat="1" ht="61.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="94"/>
       <c r="B13" s="8"/>
       <c r="C13" s="10"/>
       <c r="D13" s="10" t="s">
@@ -1595,9 +1595,9 @@
       <c r="J13" s="8"/>
       <c r="K13" s="10"/>
       <c r="L13" s="11"/>
-      <c r="M13" s="84"/>
-    </row>
-    <row r="14" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="M13" s="73"/>
+    </row>
+    <row r="14" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="46">
         <v>0</v>
       </c>
@@ -1627,9 +1627,9 @@
       <c r="J14" s="20"/>
       <c r="K14" s="20"/>
       <c r="L14" s="21"/>
-      <c r="M14" s="85"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M14" s="74"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="47">
         <f>A14+1</f>
         <v>1</v>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="L15" s="12"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="47">
         <f t="shared" ref="A16:A33" si="0">A15+1</f>
         <v>2</v>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="L16" s="12"/>
     </row>
-    <row r="17" spans="1:12" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="47">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="L17" s="12"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="47">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="L18" s="12"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="47">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="L19" s="12"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="47">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L20" s="12"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="47">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="L21" s="12"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="47">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="L22" s="12"/>
     </row>
-    <row r="23" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="47">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="L23" s="12"/>
     </row>
-    <row r="24" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="47">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="L24" s="12"/>
     </row>
-    <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="47">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="L25" s="12"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="47">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="L26" s="12"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="47">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="L27" s="12"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="47">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="L28" s="12"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="47">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="L29" s="12"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="47">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="L30" s="12"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="47">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="L31" s="12"/>
     </row>
-    <row r="32" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="47">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="L32" s="12"/>
     </row>
-    <row r="33" spans="1:13" s="15" customFormat="1" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:13" s="15" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="48">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2129,9 +2129,9 @@
       <c r="J33" s="10"/>
       <c r="K33" s="10"/>
       <c r="L33" s="14"/>
-      <c r="M33" s="87"/>
-    </row>
-    <row r="34" spans="1:13" s="18" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M33" s="76"/>
+    </row>
+    <row r="34" spans="1:13" s="18" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="49">
         <f>IF(D34=D33,A33+1,(D34*100))</f>
         <v>0</v>
@@ -2160,11 +2160,11 @@
       <c r="J34" s="17"/>
       <c r="K34" s="17"/>
       <c r="L34" s="21"/>
-      <c r="M34" s="88" t="s">
+      <c r="M34" s="77" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" s="50">
         <f t="shared" ref="A35:A45" si="2">IF(D35=D34,A34+1,(D35*100))</f>
         <v>1</v>
@@ -2192,11 +2192,11 @@
         <v>97</v>
       </c>
       <c r="L35" s="12"/>
-      <c r="M35" s="89" t="s">
+      <c r="M35" s="87" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" s="50">
         <f t="shared" si="2"/>
         <v>2</v>
@@ -2224,9 +2224,9 @@
         <v>97</v>
       </c>
       <c r="L36" s="12"/>
-      <c r="M36" s="90"/>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M36" s="88"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" s="50">
         <f t="shared" si="2"/>
         <v>3</v>
@@ -2254,9 +2254,9 @@
         <v>97</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="M37" s="90"/>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M37" s="88"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" s="50">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -2284,9 +2284,9 @@
         <v>97</v>
       </c>
       <c r="L38" s="12"/>
-      <c r="M38" s="90"/>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M38" s="88"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" s="50">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -2314,9 +2314,9 @@
         <v>97</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="90"/>
-    </row>
-    <row r="40" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M39" s="88"/>
+    </row>
+    <row r="40" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A40" s="50">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -2344,11 +2344,11 @@
         <v>97</v>
       </c>
       <c r="L40" s="12"/>
-      <c r="M40" s="91" t="s">
+      <c r="M40" s="78" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" s="50">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -2376,11 +2376,11 @@
         <v>103</v>
       </c>
       <c r="L41" s="12"/>
-      <c r="M41" s="91" t="s">
+      <c r="M41" s="78" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" s="50">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -2408,11 +2408,11 @@
         <v>103</v>
       </c>
       <c r="L42" s="12"/>
-      <c r="M42" s="86" t="s">
+      <c r="M42" s="75" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" s="50">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -2440,11 +2440,11 @@
         <v>97</v>
       </c>
       <c r="L43" s="12"/>
-      <c r="M43" s="92" t="s">
+      <c r="M43" s="79" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" s="50">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -2472,11 +2472,11 @@
         <v>97</v>
       </c>
       <c r="L44" s="12"/>
-      <c r="M44" s="86" t="s">
+      <c r="M44" s="75" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="45" spans="1:13" s="15" customFormat="1" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:13" s="15" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="51">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -2507,11 +2507,11 @@
       <c r="J45" s="10"/>
       <c r="K45" s="10"/>
       <c r="L45" s="14"/>
-      <c r="M45" s="87" t="s">
+      <c r="M45" s="76" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="46" spans="1:13" s="39" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:13" s="39" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="52">
         <f>IF(D46=D44,A44+1,(D46*100))</f>
         <v>100</v>
@@ -2537,11 +2537,11 @@
       <c r="J46" s="35"/>
       <c r="K46" s="35"/>
       <c r="L46" s="36"/>
-      <c r="M46" s="93" t="s">
+      <c r="M46" s="80" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="47" spans="1:13" s="18" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" s="18" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="49">
         <f>IF(D47=D45,A45+1,(D47*100))</f>
         <v>100</v>
@@ -2568,9 +2568,9 @@
       <c r="J47" s="17"/>
       <c r="K47" s="17"/>
       <c r="L47" s="21"/>
-      <c r="M47" s="94"/>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M47" s="81"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" s="41">
         <f t="shared" ref="A48:A112" si="3">IF(B48="","",IF(D48=D47,A47+1,(D48*100)))</f>
         <v>101</v>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="L48" s="12"/>
     </row>
-    <row r="49" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49" s="50">
         <f t="shared" si="3"/>
         <v>102</v>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="L49" s="12"/>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50" s="50">
         <f t="shared" si="3"/>
         <v>103</v>
@@ -2657,11 +2657,11 @@
         <v>97</v>
       </c>
       <c r="L50" s="12"/>
-      <c r="M50" s="86" t="s">
+      <c r="M50" s="75" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51" s="50">
         <f t="shared" si="3"/>
         <v>104</v>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="L51" s="12"/>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52" s="50">
         <f t="shared" si="3"/>
         <v>105</v>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="L52" s="12"/>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53" s="41">
         <f>IF(B53="","",IF(D53=D52,A52+1,(D53*100)))</f>
         <v>106</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="L53" s="12"/>
     </row>
-    <row r="54" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="41" t="s">
         <v>105</v>
       </c>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="L54" s="12"/>
     </row>
-    <row r="55" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="41" t="s">
         <v>105</v>
       </c>
@@ -2795,7 +2795,7 @@
       <c r="F55" s="12"/>
       <c r="L55" s="12"/>
     </row>
-    <row r="56" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="41" t="s">
         <v>105</v>
       </c>
@@ -2814,7 +2814,7 @@
       <c r="F56" s="12"/>
       <c r="L56" s="12"/>
     </row>
-    <row r="57" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="41">
         <f>IF(B57="","",IF(D57=Sheet1!D54,Sheet1!A54+1,(D57*100)))</f>
         <v>110.00000000000001</v>
@@ -2837,11 +2837,11 @@
         <v>0</v>
       </c>
       <c r="L57" s="12"/>
-      <c r="M57" s="86" t="s">
+      <c r="M57" s="75" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="58" spans="1:13" s="64" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" s="64" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="58">
         <f>IF(B58="","",IF(D58=D53,A53+1,(D58*100)))</f>
         <v>200</v>
@@ -2869,9 +2869,9 @@
       <c r="J58" s="60"/>
       <c r="K58" s="60"/>
       <c r="L58" s="63"/>
-      <c r="M58" s="95"/>
-    </row>
-    <row r="59" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="M58" s="82"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59" s="41">
         <f>IF(B59="","",IF(D59=D54,A54+1,(D59*100)))</f>
         <v>200</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L59" s="12"/>
     </row>
-    <row r="60" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60" s="41">
         <f t="shared" si="3"/>
         <v>201</v>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="L60" s="12"/>
     </row>
-    <row r="61" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61" s="41">
         <f t="shared" si="3"/>
         <v>202</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="L61" s="12"/>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62" s="41">
         <f t="shared" si="3"/>
         <v>203</v>
@@ -2970,20 +2970,20 @@
         <f t="shared" ref="D62:D124" si="6">IF(B62="","",D61)</f>
         <v>2</v>
       </c>
-      <c r="E62" s="96" t="s">
+      <c r="E62" s="84" t="s">
         <v>83</v>
       </c>
-      <c r="F62" s="96"/>
-      <c r="G62" s="96"/>
+      <c r="F62" s="84"/>
+      <c r="G62" s="84"/>
       <c r="H62" s="6" t="s">
         <v>97</v>
       </c>
       <c r="L62" s="12"/>
-      <c r="M62" s="86" t="s">
+      <c r="M62" s="75" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A63" s="41">
         <f t="shared" si="3"/>
         <v>204</v>
@@ -3001,9 +3001,12 @@
       <c r="E63" s="40">
         <v>45606</v>
       </c>
+      <c r="F63" s="12">
+        <v>45609</v>
+      </c>
       <c r="G63" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>97</v>
@@ -3013,7 +3016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64" s="41">
         <f>IF(B64="","",IF(D64=D69,A69+1,(D64*100)))</f>
         <v>207</v>
@@ -3035,7 +3038,7 @@
         <v>45605</v>
       </c>
       <c r="G64" s="6">
-        <f t="shared" ref="G64:G69" si="8">IF(B64="","",IF(AND(E64&gt;0,F64&gt;0),F64-E64,0))</f>
+        <f t="shared" ref="G64:G68" si="8">IF(B64="","",IF(AND(E64&gt;0,F64&gt;0),F64-E64,0))</f>
         <v>-1</v>
       </c>
       <c r="L64" s="12">
@@ -3043,7 +3046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65" s="41">
         <f>IF(B65="","",IF(D65=D64,A64+1,(D65*100)))</f>
         <v>208</v>
@@ -3074,7 +3077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66" s="41">
         <f>IF(B66="","",IF(D66=D65,A65+1,(D66*100)))</f>
         <v>209</v>
@@ -3102,7 +3105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67" s="41">
         <f>IF(B67="","",IF(D67=D66,A66+1,(D67*100)))</f>
         <v>210</v>
@@ -3130,7 +3133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68" s="41">
         <f>IF(B68="","",IF(D68=D63,A63+1,(D68*100)))</f>
         <v>205</v>
@@ -3158,7 +3161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A69" s="41">
         <f>IF(B69="","",IF(D69=D68,A68+1,(D69*100)))</f>
         <v>206</v>
@@ -3173,20 +3176,20 @@
         <f>IF(B69="","",D68)</f>
         <v>2</v>
       </c>
-      <c r="E69" s="96" t="s">
+      <c r="E69" s="84" t="s">
         <v>120</v>
       </c>
-      <c r="F69" s="96"/>
-      <c r="G69" s="96"/>
+      <c r="F69" s="84"/>
+      <c r="G69" s="84"/>
       <c r="L69" s="12">
         <f>IF(B69="","",IF(D69=D68,L68,IF(F69&gt;0,F69,"Not Delivered")))</f>
         <v>0</v>
       </c>
-      <c r="M69" s="86" t="s">
+      <c r="M69" s="75" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A70" s="41">
         <f t="shared" si="3"/>
         <v>207</v>
@@ -3214,7 +3217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A71" s="41">
         <f t="shared" si="3"/>
         <v>208</v>
@@ -3242,7 +3245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72" s="41">
         <f t="shared" ref="A72" si="11">IF(B72="","",IF(D72=D71,A71+1,(D72*100)))</f>
         <v>209</v>
@@ -3261,16 +3264,19 @@
         <f t="shared" ref="E72" si="13">IF(B72="","",IF(D72=D71,E71,E71+14))</f>
         <v>45606</v>
       </c>
+      <c r="F72" s="12">
+        <v>45609</v>
+      </c>
       <c r="G72" s="6">
         <f t="shared" ref="G72" si="14">IF(B72="","",IF(AND(E72&gt;0,F72&gt;0),F72-E72,0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L72" s="12">
         <f t="shared" ref="L72" si="15">IF(B72="","",IF(D72=D71,L71,IF(F72&gt;0,F72,"Not Delivered")))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="41">
         <f>IF(B73="","",IF(D73=Sheet1!D71,Sheet1!A71+1,(D73*100)))</f>
         <v>209</v>
@@ -3293,11 +3299,11 @@
         <v>0</v>
       </c>
       <c r="L73" s="12"/>
-      <c r="M73" s="86" t="s">
+      <c r="M73" s="75" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A74" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3319,7 +3325,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A75" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3341,7 +3347,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A76" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3363,7 +3369,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A77" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3385,7 +3391,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A78" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3407,7 +3413,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3429,7 +3435,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3451,7 +3457,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3473,7 +3479,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3495,7 +3501,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3517,7 +3523,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3539,7 +3545,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3561,7 +3567,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3583,7 +3589,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3605,7 +3611,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3627,7 +3633,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3649,7 +3655,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3671,7 +3677,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A91" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3693,7 +3699,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A92" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3715,7 +3721,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A93" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3737,7 +3743,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3759,7 +3765,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3781,7 +3787,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3803,7 +3809,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3825,7 +3831,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3847,7 +3853,7 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3869,7 +3875,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3891,7 +3897,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3913,7 +3919,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3935,7 +3941,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3957,7 +3963,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3979,7 +3985,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -4001,7 +4007,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A106" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -4023,7 +4029,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A107" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -4045,7 +4051,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -4067,7 +4073,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A109" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -4089,7 +4095,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -4111,7 +4117,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A111" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -4133,7 +4139,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A112" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -4155,7 +4161,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A113" s="41" t="str">
         <f t="shared" ref="A113:A170" si="16">IF(B113="","",IF(D113=D112,A112+1,(D113*100)))</f>
         <v/>
@@ -4177,7 +4183,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A114" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4199,7 +4205,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A115" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4221,7 +4227,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A116" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4243,7 +4249,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A117" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4265,7 +4271,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A118" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4287,7 +4293,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A119" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4309,7 +4315,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A120" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4331,7 +4337,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A121" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4353,7 +4359,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A122" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4375,7 +4381,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A123" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4397,7 +4403,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A124" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4419,7 +4425,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A125" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4441,7 +4447,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4463,7 +4469,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A127" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4485,7 +4491,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A128" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4507,7 +4513,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A129" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4529,7 +4535,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A130" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4551,7 +4557,7 @@
         <v/>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A131" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4573,7 +4579,7 @@
         <v/>
       </c>
     </row>
-    <row r="132" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4595,7 +4601,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A133" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4617,7 +4623,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A134" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4639,7 +4645,7 @@
         <v/>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A135" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4661,7 +4667,7 @@
         <v/>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A136" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4683,7 +4689,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A137" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4705,7 +4711,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A138" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4727,7 +4733,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A139" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4749,7 +4755,7 @@
         <v/>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A140" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4771,7 +4777,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A141" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4793,7 +4799,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A142" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4815,7 +4821,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A143" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4837,7 +4843,7 @@
         <v/>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A144" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4859,7 +4865,7 @@
         <v/>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A145" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4881,7 +4887,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A146" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4903,7 +4909,7 @@
         <v/>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A147" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4925,7 +4931,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A148" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4947,7 +4953,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A149" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4969,7 +4975,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A150" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -4991,7 +4997,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A151" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -5013,7 +5019,7 @@
         <v/>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A152" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -5035,7 +5041,7 @@
         <v/>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -5057,7 +5063,7 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -5079,7 +5085,7 @@
         <v/>
       </c>
     </row>
-    <row r="155" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -5101,7 +5107,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A156" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -5123,7 +5129,7 @@
         <v/>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -5145,7 +5151,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -5167,7 +5173,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A159" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -5189,7 +5195,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -5211,7 +5217,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A161" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -5233,7 +5239,7 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A162" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -5255,7 +5261,7 @@
         <v/>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A163" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -5277,7 +5283,7 @@
         <v/>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A164" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -5299,7 +5305,7 @@
         <v/>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A165" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -5321,7 +5327,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A166" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -5343,7 +5349,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A167" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -5365,7 +5371,7 @@
         <v/>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A168" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -5387,7 +5393,7 @@
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A169" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -5409,7 +5415,7 @@
         <v/>
       </c>
     </row>
-    <row r="170" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A170" s="41" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -5433,13 +5439,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="E69:G69"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="M35:M39"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A12:A13"/>
@@ -5452,6 +5451,13 @@
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="E69:G69"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="M35:M39"/>
   </mergeCells>
   <conditionalFormatting sqref="G10:G61 G63:G68 G70:G1048576">
     <cfRule type="colorScale" priority="1">

--- a/project requirements spreadsheet.xlsx
+++ b/project requirements spreadsheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/soapmac/Documents/GitHub/Shattered-Protocols-Text-RPG/Shattered Protocols/Shattered-Protocols-Text-RPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA6583C0-B331-9C44-9289-C2D774B87B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{535770FE-49E1-1C41-AD7D-F26A1B45554D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" xr2:uid="{CAB5D44A-E176-404C-B398-BEAD2D9E6884}"/>
   </bookViews>
@@ -940,47 +940,47 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="13" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1341,52 +1341,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="27" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="83" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="90"/>
+      <c r="B1" s="84"/>
       <c r="C1" s="25"/>
-      <c r="D1" s="95" t="s">
+      <c r="D1" s="90" t="s">
         <v>91</v>
       </c>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="95"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
+      <c r="H1" s="90"/>
+      <c r="I1" s="90"/>
+      <c r="J1" s="90"/>
+      <c r="K1" s="90"/>
       <c r="L1" s="25"/>
       <c r="M1" s="67"/>
     </row>
     <row r="2" spans="1:13" s="27" customFormat="1" ht="19" x14ac:dyDescent="0.2">
-      <c r="A2" s="91" t="s">
+      <c r="A2" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="92"/>
+      <c r="B2" s="86"/>
       <c r="C2" s="25"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="90"/>
       <c r="M2" s="68"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="42"/>
       <c r="B3" s="30"/>
       <c r="C3" s="13"/>
-      <c r="D3" s="95"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="95"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="95"/>
-      <c r="I3" s="95"/>
-      <c r="J3" s="95"/>
-      <c r="K3" s="95"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="90"/>
+      <c r="K3" s="90"/>
       <c r="L3" s="13"/>
       <c r="M3" s="69"/>
     </row>
@@ -1397,14 +1397,14 @@
       <c r="B4" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="95"/>
-      <c r="G4" s="95"/>
-      <c r="H4" s="95"/>
-      <c r="I4" s="95"/>
-      <c r="J4" s="95"/>
-      <c r="K4" s="95"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="90"/>
       <c r="M4" s="70"/>
     </row>
     <row r="5" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -1414,14 +1414,14 @@
       <c r="B5" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="95"/>
-      <c r="E5" s="95"/>
-      <c r="F5" s="95"/>
-      <c r="G5" s="95"/>
-      <c r="H5" s="95"/>
-      <c r="I5" s="95"/>
-      <c r="J5" s="95"/>
-      <c r="K5" s="95"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
+      <c r="K5" s="90"/>
       <c r="M5" s="70"/>
     </row>
     <row r="6" spans="1:13" s="7" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -1431,14 +1431,14 @@
       <c r="B6" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="95"/>
-      <c r="K6" s="95"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
+      <c r="J6" s="90"/>
+      <c r="K6" s="90"/>
       <c r="L6" s="1"/>
       <c r="M6" s="71"/>
     </row>
@@ -1458,73 +1458,73 @@
       <c r="M7" s="71"/>
     </row>
     <row r="8" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="86" t="s">
+      <c r="A8" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="86"/>
-      <c r="C8" s="86"/>
-      <c r="D8" s="86"/>
-      <c r="E8" s="86"/>
-      <c r="F8" s="86"/>
-      <c r="G8" s="86"/>
-      <c r="H8" s="86"/>
-      <c r="I8" s="86"/>
-      <c r="J8" s="86"/>
-      <c r="K8" s="86"/>
-      <c r="L8" s="86"/>
-      <c r="M8" s="86"/>
+      <c r="B8" s="91"/>
+      <c r="C8" s="91"/>
+      <c r="D8" s="91"/>
+      <c r="E8" s="91"/>
+      <c r="F8" s="91"/>
+      <c r="G8" s="91"/>
+      <c r="H8" s="91"/>
+      <c r="I8" s="91"/>
+      <c r="J8" s="91"/>
+      <c r="K8" s="91"/>
+      <c r="L8" s="91"/>
+      <c r="M8" s="91"/>
     </row>
     <row r="9" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="86" t="s">
+      <c r="C9" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="86"/>
-      <c r="E9" s="86"/>
-      <c r="F9" s="86"/>
+      <c r="D9" s="91"/>
+      <c r="E9" s="91"/>
+      <c r="F9" s="91"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="86" t="s">
+      <c r="H9" s="91" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="86"/>
-      <c r="J9" s="86"/>
-      <c r="K9" s="86"/>
-      <c r="L9" s="96" t="s">
+      <c r="I9" s="91"/>
+      <c r="J9" s="91"/>
+      <c r="K9" s="91"/>
+      <c r="L9" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="M9" s="83" t="s">
+      <c r="M9" s="93" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:13" s="7" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="85" t="s">
+      <c r="C10" s="89" t="s">
         <v>21</v>
       </c>
       <c r="D10" s="1"/>
-      <c r="E10" s="85" t="s">
+      <c r="E10" s="89" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="85" t="s">
+      <c r="F10" s="89" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="85" t="s">
+      <c r="G10" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="H10" s="85" t="s">
+      <c r="H10" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="I10" s="85" t="s">
+      <c r="I10" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="85" t="s">
+      <c r="J10" s="89" t="s">
         <v>5</v>
       </c>
       <c r="K10" s="1"/>
-      <c r="L10" s="96"/>
-      <c r="M10" s="83"/>
+      <c r="L10" s="92"/>
+      <c r="M10" s="93"/>
     </row>
     <row r="11" spans="1:13" s="7" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -1533,24 +1533,24 @@
       <c r="B11" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="85"/>
+      <c r="C11" s="89"/>
       <c r="D11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="85"/>
-      <c r="F11" s="85"/>
-      <c r="G11" s="85"/>
-      <c r="H11" s="85"/>
-      <c r="I11" s="85"/>
-      <c r="J11" s="85"/>
+      <c r="E11" s="89"/>
+      <c r="F11" s="89"/>
+      <c r="G11" s="89"/>
+      <c r="H11" s="89"/>
+      <c r="I11" s="89"/>
+      <c r="J11" s="89"/>
       <c r="K11" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="L11" s="96"/>
-      <c r="M11" s="83"/>
+      <c r="L11" s="92"/>
+      <c r="M11" s="93"/>
     </row>
     <row r="12" spans="1:13" s="57" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="93" t="s">
+      <c r="A12" s="87" t="s">
         <v>40</v>
       </c>
       <c r="B12" s="53"/>
@@ -1577,7 +1577,7 @@
       <c r="M12" s="72"/>
     </row>
     <row r="13" spans="1:13" s="3" customFormat="1" ht="61.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="94"/>
+      <c r="A13" s="88"/>
       <c r="B13" s="8"/>
       <c r="C13" s="10"/>
       <c r="D13" s="10" t="s">
@@ -2192,7 +2192,7 @@
         <v>97</v>
       </c>
       <c r="L35" s="12"/>
-      <c r="M35" s="87" t="s">
+      <c r="M35" s="95" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
         <v>97</v>
       </c>
       <c r="L36" s="12"/>
-      <c r="M36" s="88"/>
+      <c r="M36" s="96"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" s="50">
@@ -2254,7 +2254,7 @@
         <v>97</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="M37" s="88"/>
+      <c r="M37" s="96"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" s="50">
@@ -2284,7 +2284,7 @@
         <v>97</v>
       </c>
       <c r="L38" s="12"/>
-      <c r="M38" s="88"/>
+      <c r="M38" s="96"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" s="50">
@@ -2314,7 +2314,7 @@
         <v>97</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="88"/>
+      <c r="M39" s="96"/>
     </row>
     <row r="40" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A40" s="50">
@@ -2832,9 +2832,12 @@
       <c r="E57" s="40">
         <v>45603</v>
       </c>
+      <c r="F57" s="12">
+        <v>45600</v>
+      </c>
       <c r="G57" s="6">
         <f>IF(B57="","",IF(AND(E57&gt;0,F57&gt;0),F57-E57,0))</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L57" s="12"/>
       <c r="M57" s="75" t="s">
@@ -2970,11 +2973,11 @@
         <f t="shared" ref="D62:D124" si="6">IF(B62="","",D61)</f>
         <v>2</v>
       </c>
-      <c r="E62" s="84" t="s">
+      <c r="E62" s="94" t="s">
         <v>83</v>
       </c>
-      <c r="F62" s="84"/>
-      <c r="G62" s="84"/>
+      <c r="F62" s="94"/>
+      <c r="G62" s="94"/>
       <c r="H62" s="6" t="s">
         <v>97</v>
       </c>
@@ -3176,11 +3179,11 @@
         <f>IF(B69="","",D68)</f>
         <v>2</v>
       </c>
-      <c r="E69" s="84" t="s">
+      <c r="E69" s="94" t="s">
         <v>120</v>
       </c>
-      <c r="F69" s="84"/>
-      <c r="G69" s="84"/>
+      <c r="F69" s="94"/>
+      <c r="G69" s="94"/>
       <c r="L69" s="12">
         <f>IF(B69="","",IF(D69=D68,L68,IF(F69&gt;0,F69,"Not Delivered")))</f>
         <v>0</v>
@@ -3294,9 +3297,12 @@
       <c r="E73" s="40">
         <v>45607</v>
       </c>
+      <c r="F73" s="12">
+        <v>45610</v>
+      </c>
       <c r="G73" s="6">
         <f>IF(B73="","",IF(AND(E73&gt;0,F73&gt;0),F73-E73,0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L73" s="12"/>
       <c r="M73" s="75" t="s">
@@ -5439,6 +5445,12 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="M35:M39"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="E69:G69"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="J10:J11"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A12:A13"/>
@@ -5452,12 +5464,6 @@
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="M9:M11"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="E69:G69"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="M35:M39"/>
   </mergeCells>
   <conditionalFormatting sqref="G10:G61 G63:G68 G70:G1048576">
     <cfRule type="colorScale" priority="1">
